--- a/AAII_Financials/Yearly/MFC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MFC_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>MFC</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8495100</v>
+        <v>24754700</v>
       </c>
       <c r="E8" s="3">
-        <v>40660900</v>
+        <v>16783200</v>
       </c>
       <c r="F8" s="3">
-        <v>54066300</v>
+        <v>41331000</v>
       </c>
       <c r="G8" s="3">
-        <v>56577400</v>
+        <v>54957200</v>
       </c>
       <c r="H8" s="3">
-        <v>27091300</v>
+        <v>57509700</v>
       </c>
       <c r="I8" s="3">
-        <v>42401400</v>
+        <v>27537700</v>
       </c>
       <c r="J8" s="3">
+        <v>43100100</v>
+      </c>
+      <c r="K8" s="3">
         <v>38776500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24639500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>42697300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14348700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21913700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>39166700</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>-3139200</v>
+        <v>14323100</v>
       </c>
       <c r="E9" s="3">
-        <v>29956400</v>
+        <v>11097400</v>
       </c>
       <c r="F9" s="3">
-        <v>43523900</v>
+        <v>30450100</v>
       </c>
       <c r="G9" s="3">
-        <v>44175300</v>
+        <v>44241100</v>
       </c>
       <c r="H9" s="3">
-        <v>14756800</v>
+        <v>44903200</v>
       </c>
       <c r="I9" s="3">
-        <v>32229800</v>
+        <v>15000000</v>
       </c>
       <c r="J9" s="3">
+        <v>32760900</v>
+      </c>
+      <c r="K9" s="3">
         <v>28237800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16076700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>32633000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5127800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14975300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>32666700</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>11634300</v>
+        <v>10431600</v>
       </c>
       <c r="E10" s="3">
-        <v>10704500</v>
+        <v>5685800</v>
       </c>
       <c r="F10" s="3">
-        <v>10542400</v>
+        <v>10880900</v>
       </c>
       <c r="G10" s="3">
-        <v>12402100</v>
+        <v>10716100</v>
       </c>
       <c r="H10" s="3">
-        <v>12334500</v>
+        <v>12606400</v>
       </c>
       <c r="I10" s="3">
-        <v>10171600</v>
+        <v>12537700</v>
       </c>
       <c r="J10" s="3">
+        <v>10339200</v>
+      </c>
+      <c r="K10" s="3">
         <v>10538700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8562800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10064300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9220900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6938500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6500000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,23 +960,26 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>109800</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>-10900</v>
+        <v>111600</v>
       </c>
       <c r="F14" s="3">
-        <v>511100</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
+        <v>-11100</v>
+      </c>
+      <c r="G14" s="3">
+        <v>519500</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -971,24 +990,27 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>150600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>510900</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1154500</v>
+        <v>19986700</v>
       </c>
       <c r="E17" s="3">
-        <v>34019000</v>
+        <v>19102200</v>
       </c>
       <c r="F17" s="3">
-        <v>48285100</v>
+        <v>34579600</v>
       </c>
       <c r="G17" s="3">
-        <v>51096400</v>
+        <v>49080800</v>
       </c>
       <c r="H17" s="3">
-        <v>22152000</v>
+        <v>51938400</v>
       </c>
       <c r="I17" s="3">
-        <v>39755100</v>
+        <v>22517000</v>
       </c>
       <c r="J17" s="3">
+        <v>40410200</v>
+      </c>
+      <c r="K17" s="3">
         <v>35619900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21847000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>38462000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10659700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>20274900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38093500</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7340600</v>
+        <v>4768000</v>
       </c>
       <c r="E18" s="3">
-        <v>6642000</v>
+        <v>-2319000</v>
       </c>
       <c r="F18" s="3">
-        <v>5781200</v>
+        <v>6751400</v>
       </c>
       <c r="G18" s="3">
-        <v>5480900</v>
+        <v>5876400</v>
       </c>
       <c r="H18" s="3">
-        <v>4939300</v>
+        <v>5571200</v>
       </c>
       <c r="I18" s="3">
-        <v>2646300</v>
+        <v>5020700</v>
       </c>
       <c r="J18" s="3">
+        <v>2689900</v>
+      </c>
+      <c r="K18" s="3">
         <v>3156700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2792400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4235300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3689000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1638800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1073200</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,8 +1178,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1155,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>997600</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1187,177 +1220,192 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7734000</v>
+        <v>5199300</v>
       </c>
       <c r="E21" s="3">
-        <v>7028700</v>
+        <v>-936000</v>
       </c>
       <c r="F21" s="3">
-        <v>6260800</v>
+        <v>7144200</v>
       </c>
       <c r="G21" s="3">
-        <v>5938600</v>
+        <v>6363500</v>
       </c>
       <c r="H21" s="3">
-        <v>5485400</v>
+        <v>6036000</v>
       </c>
       <c r="I21" s="3">
-        <v>3055700</v>
+        <v>5575300</v>
       </c>
       <c r="J21" s="3">
+        <v>3105700</v>
+      </c>
+      <c r="K21" s="3">
         <v>3663300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3221300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4596700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4016300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1932500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1339500</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>981500</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E22" s="3">
-        <v>735000</v>
+        <v>997600</v>
       </c>
       <c r="F22" s="3">
-        <v>858600</v>
+        <v>747100</v>
       </c>
       <c r="G22" s="3">
-        <v>958900</v>
+        <v>872700</v>
       </c>
       <c r="H22" s="3">
-        <v>926900</v>
+        <v>974700</v>
       </c>
       <c r="I22" s="3">
-        <v>828100</v>
+        <v>942200</v>
       </c>
       <c r="J22" s="3">
+        <v>841700</v>
+      </c>
+      <c r="K22" s="3">
         <v>736500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>826700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>887900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>804500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>703100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>959500</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>6359200</v>
+        <v>4768000</v>
       </c>
       <c r="E23" s="3">
-        <v>5907000</v>
+        <v>-2319000</v>
       </c>
       <c r="F23" s="3">
-        <v>4922600</v>
+        <v>6004300</v>
       </c>
       <c r="G23" s="3">
-        <v>4522000</v>
+        <v>5003700</v>
       </c>
       <c r="H23" s="3">
-        <v>4012400</v>
+        <v>4596500</v>
       </c>
       <c r="I23" s="3">
-        <v>1818300</v>
+        <v>4078500</v>
       </c>
       <c r="J23" s="3">
+        <v>1848200</v>
+      </c>
+      <c r="K23" s="3">
         <v>2420200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1965800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3347500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2884500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>935700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>113700</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1137800</v>
+        <v>624400</v>
       </c>
       <c r="E24" s="3">
-        <v>881900</v>
+        <v>-856500</v>
       </c>
       <c r="F24" s="3">
-        <v>868800</v>
+        <v>896400</v>
       </c>
       <c r="G24" s="3">
-        <v>522000</v>
+        <v>883100</v>
       </c>
       <c r="H24" s="3">
-        <v>692100</v>
+        <v>530600</v>
       </c>
       <c r="I24" s="3">
-        <v>173800</v>
+        <v>703500</v>
       </c>
       <c r="J24" s="3">
+        <v>176600</v>
+      </c>
+      <c r="K24" s="3">
         <v>142500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>246300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>529900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>463400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-319200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-74500</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>5221400</v>
+        <v>4143500</v>
       </c>
       <c r="E26" s="3">
-        <v>5025100</v>
+        <v>-1462500</v>
       </c>
       <c r="F26" s="3">
-        <v>4053800</v>
+        <v>5107900</v>
       </c>
       <c r="G26" s="3">
-        <v>4000000</v>
+        <v>4120600</v>
       </c>
       <c r="H26" s="3">
-        <v>3320300</v>
+        <v>4065900</v>
       </c>
       <c r="I26" s="3">
-        <v>1644500</v>
+        <v>3375000</v>
       </c>
       <c r="J26" s="3">
+        <v>1671600</v>
+      </c>
+      <c r="K26" s="3">
         <v>2277700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1719500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2817500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2421100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1254900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>188200</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>5113800</v>
+        <v>3547200</v>
       </c>
       <c r="E27" s="3">
-        <v>5009100</v>
+        <v>-1620600</v>
       </c>
       <c r="F27" s="3">
-        <v>4144000</v>
+        <v>5091600</v>
       </c>
       <c r="G27" s="3">
-        <v>3947700</v>
+        <v>4212200</v>
       </c>
       <c r="H27" s="3">
-        <v>3134900</v>
+        <v>4012700</v>
       </c>
       <c r="I27" s="3">
-        <v>1414000</v>
+        <v>3186500</v>
       </c>
       <c r="J27" s="3">
+        <v>1437300</v>
+      </c>
+      <c r="K27" s="3">
         <v>2032700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1558000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2646400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2292500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1227000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>33800</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1538,14 +1598,14 @@
       <c r="F29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H29" s="3">
-        <v>232600</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>236500</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>8</v>
@@ -1553,21 +1613,24 @@
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
+      <c r="L29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M29" s="3">
         <v>3100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>16200</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>51200</v>
       </c>
-      <c r="O29" s="3" t="s">
+      <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,9 +1715,12 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1659,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-997600</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -1691,51 +1760,57 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>5113800</v>
+        <v>3547200</v>
       </c>
       <c r="E33" s="3">
-        <v>5009100</v>
+        <v>-1620600</v>
       </c>
       <c r="F33" s="3">
-        <v>4144000</v>
+        <v>5091600</v>
       </c>
       <c r="G33" s="3">
-        <v>3947700</v>
+        <v>4212200</v>
       </c>
       <c r="H33" s="3">
-        <v>3367500</v>
+        <v>4012700</v>
       </c>
       <c r="I33" s="3">
-        <v>1414000</v>
+        <v>3423000</v>
       </c>
       <c r="J33" s="3">
+        <v>1437300</v>
+      </c>
+      <c r="K33" s="3">
         <v>2032700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1558000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2649500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2308700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1278200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>33800</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>5113800</v>
+        <v>3547200</v>
       </c>
       <c r="E35" s="3">
-        <v>5009100</v>
+        <v>-1620600</v>
       </c>
       <c r="F35" s="3">
-        <v>4144000</v>
+        <v>5091600</v>
       </c>
       <c r="G35" s="3">
-        <v>3947700</v>
+        <v>4212200</v>
       </c>
       <c r="H35" s="3">
-        <v>3367500</v>
+        <v>4012700</v>
       </c>
       <c r="I35" s="3">
-        <v>1414000</v>
+        <v>3423000</v>
       </c>
       <c r="J35" s="3">
+        <v>1437300</v>
+      </c>
+      <c r="K35" s="3">
         <v>2032700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1558000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2649500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2308700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1278200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>33800</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,50 +1986,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>13924400</v>
+        <v>15029600</v>
       </c>
       <c r="E41" s="3">
-        <v>16426100</v>
+        <v>14153900</v>
       </c>
       <c r="F41" s="3">
-        <v>19023700</v>
+        <v>16696700</v>
       </c>
       <c r="G41" s="3">
-        <v>14758300</v>
+        <v>19337200</v>
       </c>
       <c r="H41" s="3">
-        <v>11788500</v>
+        <v>15001500</v>
       </c>
       <c r="I41" s="3">
-        <v>11606700</v>
+        <v>11982700</v>
       </c>
       <c r="J41" s="3">
+        <v>11798000</v>
+      </c>
+      <c r="K41" s="3">
         <v>11014900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13429100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16548100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10492600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10076800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9843300</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1984,26 +2073,29 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>1052700</v>
+      <c r="D43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E43" s="3">
-        <v>940800</v>
+        <v>1070100</v>
       </c>
       <c r="F43" s="3">
-        <v>1049800</v>
+        <v>956300</v>
       </c>
       <c r="G43" s="3">
-        <v>1006900</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>8</v>
+        <v>1067100</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1023500</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>8</v>
@@ -2017,8 +2109,8 @@
       <c r="L43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2026,9 +2118,12 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2068,9 +2163,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2110,9 +2208,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2152,51 +2253,57 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>282484000</v>
+        <v>293392000</v>
       </c>
       <c r="E47" s="3">
-        <v>294079000</v>
+        <v>287139000</v>
       </c>
       <c r="F47" s="3">
-        <v>279761000</v>
+        <v>298924000</v>
       </c>
       <c r="G47" s="3">
-        <v>260435000</v>
+        <v>284371000</v>
       </c>
       <c r="H47" s="3">
-        <v>245329000</v>
+        <v>264726000</v>
       </c>
       <c r="I47" s="3">
-        <v>231376000</v>
+        <v>249371000</v>
       </c>
       <c r="J47" s="3">
+        <v>235189000</v>
+      </c>
+      <c r="K47" s="3">
         <v>222987000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>218787000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>194874000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>152474000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>155275000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>148586000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2209,11 +2316,11 @@
       <c r="F48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G48" s="3">
-        <v>277000</v>
-      </c>
-      <c r="H48" s="3" t="s">
+      <c r="G48" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="H48" s="3">
+        <v>281600</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>8</v>
@@ -2230,57 +2337,63 @@
       <c r="M48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="N48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>15294800</v>
+        <v>7619000</v>
       </c>
       <c r="E49" s="3">
-        <v>7208300</v>
+        <v>15546900</v>
       </c>
       <c r="F49" s="3">
-        <v>7218500</v>
+        <v>7327100</v>
       </c>
       <c r="G49" s="3">
-        <v>7251900</v>
+        <v>7337400</v>
       </c>
       <c r="H49" s="3">
-        <v>7340600</v>
+        <v>7371400</v>
       </c>
       <c r="I49" s="3">
-        <v>7153800</v>
+        <v>7461600</v>
       </c>
       <c r="J49" s="3">
+        <v>7271700</v>
+      </c>
+      <c r="K49" s="3">
         <v>7347900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7046100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4287200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4078500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7698000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4180700</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4876800</v>
+        <v>4980100</v>
       </c>
       <c r="E52" s="3">
-        <v>3819700</v>
+        <v>4957100</v>
       </c>
       <c r="F52" s="3">
-        <v>3520200</v>
+        <v>3882700</v>
       </c>
       <c r="G52" s="3">
-        <v>3325300</v>
+        <v>3578200</v>
       </c>
       <c r="H52" s="3">
-        <v>3139200</v>
+        <v>3380100</v>
       </c>
       <c r="I52" s="3">
-        <v>3321700</v>
+        <v>3191000</v>
       </c>
       <c r="J52" s="3">
+        <v>3376400</v>
+      </c>
+      <c r="K52" s="3">
         <v>3227200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3053700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2613400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2127000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2391600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1349800</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>606100000</v>
+        <v>647040000</v>
       </c>
       <c r="E54" s="3">
-        <v>667136000</v>
+        <v>616088000</v>
       </c>
       <c r="F54" s="3">
-        <v>640023000</v>
+        <v>678129000</v>
       </c>
       <c r="G54" s="3">
-        <v>588246000</v>
+        <v>650569000</v>
       </c>
       <c r="H54" s="3">
-        <v>545455000</v>
+        <v>597939000</v>
       </c>
       <c r="I54" s="3">
-        <v>530378000</v>
+        <v>554443000</v>
       </c>
       <c r="J54" s="3">
+        <v>539118000</v>
+      </c>
+      <c r="K54" s="3">
         <v>523942000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>529088000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>454863000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>395401000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>365102000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>354905000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,8 +2654,9 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2566,9 +2696,12 @@
       <c r="O57" s="3">
         <v>0</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2608,51 +2741,57 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>800147000</v>
+        <v>577745000</v>
       </c>
       <c r="E59" s="3">
-        <v>316801000</v>
+        <v>813332000</v>
       </c>
       <c r="F59" s="3">
-        <v>293058000</v>
+        <v>322022000</v>
       </c>
       <c r="G59" s="3">
-        <v>275156000</v>
+        <v>297887000</v>
       </c>
       <c r="H59" s="3">
-        <v>252038000</v>
+        <v>279690000</v>
       </c>
       <c r="I59" s="3">
-        <v>258108000</v>
+        <v>256191000</v>
       </c>
       <c r="J59" s="3">
+        <v>262361000</v>
+      </c>
+      <c r="K59" s="3">
         <v>251392000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>258201000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>223771000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>191862000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>314510000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>296767000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2692,93 +2831,102 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8982900</v>
+        <v>9413300</v>
       </c>
       <c r="E61" s="3">
-        <v>8623800</v>
+        <v>9131000</v>
       </c>
       <c r="F61" s="3">
-        <v>10173100</v>
+        <v>8765900</v>
       </c>
       <c r="G61" s="3">
-        <v>8777200</v>
+        <v>10340700</v>
       </c>
       <c r="H61" s="3">
-        <v>9815400</v>
+        <v>8921800</v>
       </c>
       <c r="I61" s="3">
-        <v>9576200</v>
+        <v>9977100</v>
       </c>
       <c r="J61" s="3">
+        <v>9734000</v>
+      </c>
+      <c r="K61" s="3">
         <v>9361000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7169200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7309600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7051600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6736700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13169000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1116700</v>
+        <v>1254100</v>
       </c>
       <c r="E62" s="3">
-        <v>2013100</v>
+        <v>1135100</v>
       </c>
       <c r="F62" s="3">
-        <v>1900400</v>
+        <v>2046300</v>
       </c>
       <c r="G62" s="3">
-        <v>1433700</v>
+        <v>1931700</v>
       </c>
       <c r="H62" s="3">
-        <v>1318800</v>
+        <v>1457300</v>
       </c>
       <c r="I62" s="3">
-        <v>931300</v>
+        <v>1340500</v>
       </c>
       <c r="J62" s="3">
+        <v>946600</v>
+      </c>
+      <c r="K62" s="3">
         <v>988000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>927300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>964000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>475000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>453900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>588500</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>572077000</v>
+        <v>612089000</v>
       </c>
       <c r="E66" s="3">
-        <v>625569000</v>
+        <v>581504000</v>
       </c>
       <c r="F66" s="3">
-        <v>602544000</v>
+        <v>635877000</v>
       </c>
       <c r="G66" s="3">
-        <v>552698000</v>
+        <v>612473000</v>
       </c>
       <c r="H66" s="3">
-        <v>511970000</v>
+        <v>561806000</v>
       </c>
       <c r="I66" s="3">
-        <v>500400000</v>
+        <v>520406000</v>
       </c>
       <c r="J66" s="3">
+        <v>508646000</v>
+      </c>
+      <c r="K66" s="3">
         <v>493350000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>498043000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>428593000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>373340000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>346389000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>336111000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,51 +3210,57 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>4841900</v>
+        <v>4921700</v>
       </c>
       <c r="E70" s="3">
-        <v>4639100</v>
+        <v>4921700</v>
       </c>
       <c r="F70" s="3">
-        <v>2778600</v>
+        <v>4715500</v>
       </c>
       <c r="G70" s="3">
-        <v>2778600</v>
+        <v>2824400</v>
       </c>
       <c r="H70" s="3">
-        <v>2778600</v>
+        <v>2824400</v>
       </c>
       <c r="I70" s="3">
+        <v>2824400</v>
+      </c>
+      <c r="J70" s="3">
+        <v>2643400</v>
+      </c>
+      <c r="K70" s="3">
         <v>2600500</v>
       </c>
-      <c r="J70" s="3">
-        <v>2600500</v>
-      </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>2022100</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>2114100</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>2073100</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>3759400</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>1392800</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2869500</v>
+        <v>3561200</v>
       </c>
       <c r="E72" s="3">
-        <v>17078900</v>
+        <v>2916800</v>
       </c>
       <c r="F72" s="3">
-        <v>13731000</v>
+        <v>17360400</v>
       </c>
       <c r="G72" s="3">
-        <v>11259900</v>
+        <v>13957300</v>
       </c>
       <c r="H72" s="3">
-        <v>9235900</v>
+        <v>11445500</v>
       </c>
       <c r="I72" s="3">
-        <v>7330400</v>
+        <v>9388100</v>
       </c>
       <c r="J72" s="3">
+        <v>7451200</v>
+      </c>
+      <c r="K72" s="3">
         <v>7094900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6305700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5985200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4075400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2451100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1921300</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>29181400</v>
+        <v>30029600</v>
       </c>
       <c r="E76" s="3">
-        <v>36927700</v>
+        <v>29662300</v>
       </c>
       <c r="F76" s="3">
-        <v>34699500</v>
+        <v>37536300</v>
       </c>
       <c r="G76" s="3">
-        <v>32768600</v>
+        <v>35271300</v>
       </c>
       <c r="H76" s="3">
-        <v>30706000</v>
+        <v>33308500</v>
       </c>
       <c r="I76" s="3">
-        <v>27377000</v>
+        <v>31212000</v>
       </c>
       <c r="J76" s="3">
+        <v>27828100</v>
+      </c>
+      <c r="K76" s="3">
         <v>27992100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>29023000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>24155200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19987600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14953500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17401200</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>5113800</v>
+        <v>3547200</v>
       </c>
       <c r="E81" s="3">
-        <v>5009100</v>
+        <v>-1620600</v>
       </c>
       <c r="F81" s="3">
-        <v>4144000</v>
+        <v>5091600</v>
       </c>
       <c r="G81" s="3">
-        <v>3947700</v>
+        <v>4212200</v>
       </c>
       <c r="H81" s="3">
-        <v>3367500</v>
+        <v>4012700</v>
       </c>
       <c r="I81" s="3">
-        <v>1414000</v>
+        <v>3423000</v>
       </c>
       <c r="J81" s="3">
+        <v>1437300</v>
+      </c>
+      <c r="K81" s="3">
         <v>2032700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1558000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2649500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2308700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1278200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>33800</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>391100</v>
+        <v>429400</v>
       </c>
       <c r="E83" s="3">
-        <v>384600</v>
+        <v>383500</v>
       </c>
       <c r="F83" s="3">
-        <v>476900</v>
+        <v>390900</v>
       </c>
       <c r="G83" s="3">
-        <v>455100</v>
+        <v>484800</v>
       </c>
       <c r="H83" s="3">
-        <v>543100</v>
+        <v>462600</v>
       </c>
       <c r="I83" s="3">
-        <v>407100</v>
+        <v>552000</v>
       </c>
       <c r="J83" s="3">
+        <v>413800</v>
+      </c>
+      <c r="K83" s="3">
         <v>503800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>435500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>362700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>327900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>293600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>265000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>12893500</v>
+        <v>15092400</v>
       </c>
       <c r="E89" s="3">
-        <v>16833900</v>
+        <v>12287900</v>
       </c>
       <c r="F89" s="3">
-        <v>14575100</v>
+        <v>17111300</v>
       </c>
       <c r="G89" s="3">
-        <v>14934200</v>
+        <v>14815300</v>
       </c>
       <c r="H89" s="3">
-        <v>13949900</v>
+        <v>15180300</v>
       </c>
       <c r="I89" s="3">
-        <v>12934200</v>
+        <v>14179700</v>
       </c>
       <c r="J89" s="3">
+        <v>13147400</v>
+      </c>
+      <c r="K89" s="3">
         <v>12385300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7759400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8483300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7315600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8126400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8349100</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,8 +4021,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3843,9 +4063,12 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-13529700</v>
+        <v>-10138900</v>
       </c>
       <c r="E94" s="3">
-        <v>-17769600</v>
+        <v>-13597400</v>
       </c>
       <c r="F94" s="3">
-        <v>-10285700</v>
+        <v>-18062400</v>
       </c>
       <c r="G94" s="3">
-        <v>-10054500</v>
+        <v>-10455200</v>
       </c>
       <c r="H94" s="3">
-        <v>-13814600</v>
+        <v>-10220200</v>
       </c>
       <c r="I94" s="3">
-        <v>-11840800</v>
+        <v>-14042300</v>
       </c>
       <c r="J94" s="3">
+        <v>-12035900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-16531500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10410700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3192000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8119300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8156500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8263900</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2026200</v>
+        <v>-2196300</v>
       </c>
       <c r="E96" s="3">
-        <v>-1817500</v>
+        <v>-2059600</v>
       </c>
       <c r="F96" s="3">
-        <v>-1701200</v>
+        <v>-1847500</v>
       </c>
       <c r="G96" s="3">
-        <v>-1016400</v>
+        <v>-1729200</v>
       </c>
       <c r="H96" s="3">
-        <v>-1299900</v>
+        <v>-1033100</v>
       </c>
       <c r="I96" s="3">
-        <v>-1294100</v>
+        <v>-1321300</v>
       </c>
       <c r="J96" s="3">
+        <v>-1315400</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1158100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1071500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-714400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-585800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-551800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-550800</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2184700</v>
+        <v>-3726000</v>
       </c>
       <c r="E100" s="3">
-        <v>-1488200</v>
+        <v>-1557800</v>
       </c>
       <c r="F100" s="3">
-        <v>482000</v>
+        <v>-1512700</v>
       </c>
       <c r="G100" s="3">
-        <v>-1512200</v>
+        <v>490000</v>
       </c>
       <c r="H100" s="3">
-        <v>-526400</v>
+        <v>-1537100</v>
       </c>
       <c r="I100" s="3">
-        <v>10200</v>
+        <v>-535000</v>
       </c>
       <c r="J100" s="3">
+        <v>10300</v>
+      </c>
+      <c r="K100" s="3">
         <v>2389000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1506200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>16500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>537300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>557100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>503200</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>425300</v>
+        <v>-304500</v>
       </c>
       <c r="E101" s="3">
-        <v>-231900</v>
+        <v>432300</v>
       </c>
       <c r="F101" s="3">
-        <v>-383900</v>
+        <v>-235700</v>
       </c>
       <c r="G101" s="3">
-        <v>-338800</v>
+        <v>-390200</v>
       </c>
       <c r="H101" s="3">
-        <v>597600</v>
+        <v>-344400</v>
       </c>
       <c r="I101" s="3">
-        <v>-478400</v>
+        <v>607400</v>
       </c>
       <c r="J101" s="3">
+        <v>-486300</v>
+      </c>
+      <c r="K101" s="3">
         <v>-252300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1578300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>620200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>368700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-160300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>147500</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2395500</v>
+        <v>923000</v>
       </c>
       <c r="E102" s="3">
-        <v>-2655800</v>
+        <v>-2435000</v>
       </c>
       <c r="F102" s="3">
-        <v>4387500</v>
+        <v>-2699500</v>
       </c>
       <c r="G102" s="3">
-        <v>3028700</v>
+        <v>4459800</v>
       </c>
       <c r="H102" s="3">
-        <v>206500</v>
+        <v>3078600</v>
       </c>
       <c r="I102" s="3">
-        <v>625200</v>
+        <v>209900</v>
       </c>
       <c r="J102" s="3">
+        <v>635500</v>
+      </c>
+      <c r="K102" s="3">
         <v>-2009500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2579200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5927900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>102400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>366600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>736000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/MFC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MFC_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>24754700</v>
+        <v>24412000</v>
       </c>
       <c r="E8" s="3">
-        <v>16783200</v>
+        <v>16550900</v>
       </c>
       <c r="F8" s="3">
-        <v>41331000</v>
+        <v>40758800</v>
       </c>
       <c r="G8" s="3">
-        <v>54957200</v>
+        <v>54196400</v>
       </c>
       <c r="H8" s="3">
-        <v>57509700</v>
+        <v>56713600</v>
       </c>
       <c r="I8" s="3">
-        <v>27537700</v>
+        <v>27156500</v>
       </c>
       <c r="J8" s="3">
-        <v>43100100</v>
+        <v>42503500</v>
       </c>
       <c r="K8" s="3">
         <v>38776500</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>14323100</v>
+        <v>14124800</v>
       </c>
       <c r="E9" s="3">
-        <v>11097400</v>
+        <v>10943800</v>
       </c>
       <c r="F9" s="3">
-        <v>30450100</v>
+        <v>30028600</v>
       </c>
       <c r="G9" s="3">
-        <v>44241100</v>
+        <v>43628700</v>
       </c>
       <c r="H9" s="3">
-        <v>44903200</v>
+        <v>44281600</v>
       </c>
       <c r="I9" s="3">
-        <v>15000000</v>
+        <v>14792400</v>
       </c>
       <c r="J9" s="3">
-        <v>32760900</v>
+        <v>32307400</v>
       </c>
       <c r="K9" s="3">
         <v>28237800</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>10431600</v>
+        <v>10287200</v>
       </c>
       <c r="E10" s="3">
-        <v>5685800</v>
+        <v>5607100</v>
       </c>
       <c r="F10" s="3">
-        <v>10880900</v>
+        <v>10730300</v>
       </c>
       <c r="G10" s="3">
-        <v>10716100</v>
+        <v>10567700</v>
       </c>
       <c r="H10" s="3">
-        <v>12606400</v>
+        <v>12431900</v>
       </c>
       <c r="I10" s="3">
-        <v>12537700</v>
+        <v>12364100</v>
       </c>
       <c r="J10" s="3">
-        <v>10339200</v>
+        <v>10196100</v>
       </c>
       <c r="K10" s="3">
         <v>10538700</v>
@@ -973,13 +973,13 @@
         <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>111600</v>
+        <v>110000</v>
       </c>
       <c r="F14" s="3">
-        <v>-11100</v>
+        <v>-10900</v>
       </c>
       <c r="G14" s="3">
-        <v>519500</v>
+        <v>512300</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>19986700</v>
+        <v>19710000</v>
       </c>
       <c r="E17" s="3">
-        <v>19102200</v>
+        <v>18837700</v>
       </c>
       <c r="F17" s="3">
-        <v>34579600</v>
+        <v>34100900</v>
       </c>
       <c r="G17" s="3">
-        <v>49080800</v>
+        <v>48401300</v>
       </c>
       <c r="H17" s="3">
-        <v>51938400</v>
+        <v>51219400</v>
       </c>
       <c r="I17" s="3">
-        <v>22517000</v>
+        <v>22205300</v>
       </c>
       <c r="J17" s="3">
-        <v>40410200</v>
+        <v>39850800</v>
       </c>
       <c r="K17" s="3">
         <v>35619900</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4768000</v>
+        <v>4702000</v>
       </c>
       <c r="E18" s="3">
-        <v>-2319000</v>
+        <v>-2286800</v>
       </c>
       <c r="F18" s="3">
-        <v>6751400</v>
+        <v>6658000</v>
       </c>
       <c r="G18" s="3">
-        <v>5876400</v>
+        <v>5795100</v>
       </c>
       <c r="H18" s="3">
-        <v>5571200</v>
+        <v>5494100</v>
       </c>
       <c r="I18" s="3">
-        <v>5020700</v>
+        <v>4951200</v>
       </c>
       <c r="J18" s="3">
-        <v>2689900</v>
+        <v>2652700</v>
       </c>
       <c r="K18" s="3">
         <v>3156700</v>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>997600</v>
+        <v>983800</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5199300</v>
+        <v>5124300</v>
       </c>
       <c r="E21" s="3">
-        <v>-936000</v>
+        <v>-925800</v>
       </c>
       <c r="F21" s="3">
-        <v>7144200</v>
+        <v>7042500</v>
       </c>
       <c r="G21" s="3">
-        <v>6363500</v>
+        <v>6271900</v>
       </c>
       <c r="H21" s="3">
-        <v>6036000</v>
+        <v>5949200</v>
       </c>
       <c r="I21" s="3">
-        <v>5575300</v>
+        <v>5494200</v>
       </c>
       <c r="J21" s="3">
-        <v>3105700</v>
+        <v>3059800</v>
       </c>
       <c r="K21" s="3">
         <v>3663300</v>
@@ -1278,22 +1278,22 @@
         <v>8</v>
       </c>
       <c r="E22" s="3">
-        <v>997600</v>
+        <v>983800</v>
       </c>
       <c r="F22" s="3">
-        <v>747100</v>
+        <v>736800</v>
       </c>
       <c r="G22" s="3">
-        <v>872700</v>
+        <v>860700</v>
       </c>
       <c r="H22" s="3">
-        <v>974700</v>
+        <v>961200</v>
       </c>
       <c r="I22" s="3">
-        <v>942200</v>
+        <v>929200</v>
       </c>
       <c r="J22" s="3">
-        <v>841700</v>
+        <v>830100</v>
       </c>
       <c r="K22" s="3">
         <v>736500</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4768000</v>
+        <v>4702000</v>
       </c>
       <c r="E23" s="3">
-        <v>-2319000</v>
+        <v>-2286800</v>
       </c>
       <c r="F23" s="3">
-        <v>6004300</v>
+        <v>5921200</v>
       </c>
       <c r="G23" s="3">
-        <v>5003700</v>
+        <v>4934400</v>
       </c>
       <c r="H23" s="3">
-        <v>4596500</v>
+        <v>4532900</v>
       </c>
       <c r="I23" s="3">
-        <v>4078500</v>
+        <v>4022000</v>
       </c>
       <c r="J23" s="3">
-        <v>1848200</v>
+        <v>1822600</v>
       </c>
       <c r="K23" s="3">
         <v>2420200</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>624400</v>
+        <v>615800</v>
       </c>
       <c r="E24" s="3">
-        <v>-856500</v>
+        <v>-844600</v>
       </c>
       <c r="F24" s="3">
-        <v>896400</v>
+        <v>884000</v>
       </c>
       <c r="G24" s="3">
-        <v>883100</v>
+        <v>870900</v>
       </c>
       <c r="H24" s="3">
-        <v>530600</v>
+        <v>523200</v>
       </c>
       <c r="I24" s="3">
-        <v>703500</v>
+        <v>693800</v>
       </c>
       <c r="J24" s="3">
-        <v>176600</v>
+        <v>174200</v>
       </c>
       <c r="K24" s="3">
         <v>142500</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4143500</v>
+        <v>4086200</v>
       </c>
       <c r="E26" s="3">
-        <v>-1462500</v>
+        <v>-1442200</v>
       </c>
       <c r="F26" s="3">
-        <v>5107900</v>
+        <v>5037200</v>
       </c>
       <c r="G26" s="3">
-        <v>4120600</v>
+        <v>4063600</v>
       </c>
       <c r="H26" s="3">
-        <v>4065900</v>
+        <v>4009600</v>
       </c>
       <c r="I26" s="3">
-        <v>3375000</v>
+        <v>3328200</v>
       </c>
       <c r="J26" s="3">
-        <v>1671600</v>
+        <v>1648500</v>
       </c>
       <c r="K26" s="3">
         <v>2277700</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>3547200</v>
+        <v>3498000</v>
       </c>
       <c r="E27" s="3">
-        <v>-1620600</v>
+        <v>-1598200</v>
       </c>
       <c r="F27" s="3">
-        <v>5091600</v>
+        <v>5021200</v>
       </c>
       <c r="G27" s="3">
-        <v>4212200</v>
+        <v>4153900</v>
       </c>
       <c r="H27" s="3">
-        <v>4012700</v>
+        <v>3957200</v>
       </c>
       <c r="I27" s="3">
-        <v>3186500</v>
+        <v>3142400</v>
       </c>
       <c r="J27" s="3">
-        <v>1437300</v>
+        <v>1417400</v>
       </c>
       <c r="K27" s="3">
         <v>2032700</v>
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>236500</v>
+        <v>233200</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>8</v>
@@ -1728,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-997600</v>
+        <v>-983800</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>3547200</v>
+        <v>3498000</v>
       </c>
       <c r="E33" s="3">
-        <v>-1620600</v>
+        <v>-1598200</v>
       </c>
       <c r="F33" s="3">
-        <v>5091600</v>
+        <v>5021200</v>
       </c>
       <c r="G33" s="3">
-        <v>4212200</v>
+        <v>4153900</v>
       </c>
       <c r="H33" s="3">
-        <v>4012700</v>
+        <v>3957200</v>
       </c>
       <c r="I33" s="3">
-        <v>3423000</v>
+        <v>3375600</v>
       </c>
       <c r="J33" s="3">
-        <v>1437300</v>
+        <v>1417400</v>
       </c>
       <c r="K33" s="3">
         <v>2032700</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>3547200</v>
+        <v>3498000</v>
       </c>
       <c r="E35" s="3">
-        <v>-1620600</v>
+        <v>-1598200</v>
       </c>
       <c r="F35" s="3">
-        <v>5091600</v>
+        <v>5021200</v>
       </c>
       <c r="G35" s="3">
-        <v>4212200</v>
+        <v>4153900</v>
       </c>
       <c r="H35" s="3">
-        <v>4012700</v>
+        <v>3957200</v>
       </c>
       <c r="I35" s="3">
-        <v>3423000</v>
+        <v>3375600</v>
       </c>
       <c r="J35" s="3">
-        <v>1437300</v>
+        <v>1417400</v>
       </c>
       <c r="K35" s="3">
         <v>2032700</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>15029600</v>
+        <v>14821500</v>
       </c>
       <c r="E41" s="3">
-        <v>14153900</v>
+        <v>13957900</v>
       </c>
       <c r="F41" s="3">
-        <v>16696700</v>
+        <v>16465600</v>
       </c>
       <c r="G41" s="3">
-        <v>19337200</v>
+        <v>19069500</v>
       </c>
       <c r="H41" s="3">
-        <v>15001500</v>
+        <v>14793800</v>
       </c>
       <c r="I41" s="3">
-        <v>11982700</v>
+        <v>11816800</v>
       </c>
       <c r="J41" s="3">
-        <v>11798000</v>
+        <v>11634700</v>
       </c>
       <c r="K41" s="3">
         <v>11014900</v>
@@ -2086,16 +2086,16 @@
         <v>8</v>
       </c>
       <c r="E43" s="3">
-        <v>1070100</v>
+        <v>1055200</v>
       </c>
       <c r="F43" s="3">
-        <v>956300</v>
+        <v>943000</v>
       </c>
       <c r="G43" s="3">
-        <v>1067100</v>
+        <v>1052300</v>
       </c>
       <c r="H43" s="3">
-        <v>1023500</v>
+        <v>1009300</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>8</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>293392000</v>
+        <v>289330000</v>
       </c>
       <c r="E47" s="3">
-        <v>287139000</v>
+        <v>283164000</v>
       </c>
       <c r="F47" s="3">
-        <v>298924000</v>
+        <v>294786000</v>
       </c>
       <c r="G47" s="3">
-        <v>284371000</v>
+        <v>280434000</v>
       </c>
       <c r="H47" s="3">
-        <v>264726000</v>
+        <v>261062000</v>
       </c>
       <c r="I47" s="3">
-        <v>249371000</v>
+        <v>245919000</v>
       </c>
       <c r="J47" s="3">
-        <v>235189000</v>
+        <v>231933000</v>
       </c>
       <c r="K47" s="3">
         <v>222987000</v>
@@ -2320,7 +2320,7 @@
         <v>8</v>
       </c>
       <c r="H48" s="3">
-        <v>281600</v>
+        <v>277700</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>8</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7619000</v>
+        <v>7513500</v>
       </c>
       <c r="E49" s="3">
-        <v>15546900</v>
+        <v>15331700</v>
       </c>
       <c r="F49" s="3">
-        <v>7327100</v>
+        <v>7225700</v>
       </c>
       <c r="G49" s="3">
-        <v>7337400</v>
+        <v>7235900</v>
       </c>
       <c r="H49" s="3">
-        <v>7371400</v>
+        <v>7269400</v>
       </c>
       <c r="I49" s="3">
-        <v>7461600</v>
+        <v>7358300</v>
       </c>
       <c r="J49" s="3">
-        <v>7271700</v>
+        <v>7171000</v>
       </c>
       <c r="K49" s="3">
         <v>7347900</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4980100</v>
+        <v>4911100</v>
       </c>
       <c r="E52" s="3">
-        <v>4957100</v>
+        <v>4888500</v>
       </c>
       <c r="F52" s="3">
-        <v>3882700</v>
+        <v>3828900</v>
       </c>
       <c r="G52" s="3">
-        <v>3578200</v>
+        <v>3528700</v>
       </c>
       <c r="H52" s="3">
-        <v>3380100</v>
+        <v>3333300</v>
       </c>
       <c r="I52" s="3">
-        <v>3191000</v>
+        <v>3146800</v>
       </c>
       <c r="J52" s="3">
-        <v>3376400</v>
+        <v>3329700</v>
       </c>
       <c r="K52" s="3">
         <v>3227200</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>647040000</v>
+        <v>638083000</v>
       </c>
       <c r="E54" s="3">
-        <v>616088000</v>
+        <v>607559000</v>
       </c>
       <c r="F54" s="3">
-        <v>678129000</v>
+        <v>668742000</v>
       </c>
       <c r="G54" s="3">
-        <v>650569000</v>
+        <v>641563000</v>
       </c>
       <c r="H54" s="3">
-        <v>597939000</v>
+        <v>589662000</v>
       </c>
       <c r="I54" s="3">
-        <v>554443000</v>
+        <v>546768000</v>
       </c>
       <c r="J54" s="3">
-        <v>539118000</v>
+        <v>531655000</v>
       </c>
       <c r="K54" s="3">
         <v>523942000</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>577745000</v>
+        <v>569747000</v>
       </c>
       <c r="E59" s="3">
-        <v>813332000</v>
+        <v>802073000</v>
       </c>
       <c r="F59" s="3">
-        <v>322022000</v>
+        <v>317564000</v>
       </c>
       <c r="G59" s="3">
-        <v>297887000</v>
+        <v>293763000</v>
       </c>
       <c r="H59" s="3">
-        <v>279690000</v>
+        <v>275818000</v>
       </c>
       <c r="I59" s="3">
-        <v>256191000</v>
+        <v>252644000</v>
       </c>
       <c r="J59" s="3">
-        <v>262361000</v>
+        <v>258729000</v>
       </c>
       <c r="K59" s="3">
         <v>251392000</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>9413300</v>
+        <v>9282900</v>
       </c>
       <c r="E61" s="3">
-        <v>9131000</v>
+        <v>9004600</v>
       </c>
       <c r="F61" s="3">
-        <v>8765900</v>
+        <v>8644600</v>
       </c>
       <c r="G61" s="3">
-        <v>10340700</v>
+        <v>10197500</v>
       </c>
       <c r="H61" s="3">
-        <v>8921800</v>
+        <v>8798300</v>
       </c>
       <c r="I61" s="3">
-        <v>9977100</v>
+        <v>9839000</v>
       </c>
       <c r="J61" s="3">
-        <v>9734000</v>
+        <v>9599200</v>
       </c>
       <c r="K61" s="3">
         <v>9361000</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1254100</v>
+        <v>1236700</v>
       </c>
       <c r="E62" s="3">
-        <v>1135100</v>
+        <v>1119400</v>
       </c>
       <c r="F62" s="3">
-        <v>2046300</v>
+        <v>2017900</v>
       </c>
       <c r="G62" s="3">
-        <v>1931700</v>
+        <v>1905000</v>
       </c>
       <c r="H62" s="3">
-        <v>1457300</v>
+        <v>1437100</v>
       </c>
       <c r="I62" s="3">
-        <v>1340500</v>
+        <v>1322000</v>
       </c>
       <c r="J62" s="3">
-        <v>946600</v>
+        <v>933500</v>
       </c>
       <c r="K62" s="3">
         <v>988000</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>612089000</v>
+        <v>603616000</v>
       </c>
       <c r="E66" s="3">
-        <v>581504000</v>
+        <v>573454000</v>
       </c>
       <c r="F66" s="3">
-        <v>635877000</v>
+        <v>627075000</v>
       </c>
       <c r="G66" s="3">
-        <v>612473000</v>
+        <v>603995000</v>
       </c>
       <c r="H66" s="3">
-        <v>561806000</v>
+        <v>554029000</v>
       </c>
       <c r="I66" s="3">
-        <v>520406000</v>
+        <v>513202000</v>
       </c>
       <c r="J66" s="3">
-        <v>508646000</v>
+        <v>501605000</v>
       </c>
       <c r="K66" s="3">
         <v>493350000</v>
@@ -3220,25 +3220,25 @@
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>4921700</v>
+        <v>4853500</v>
       </c>
       <c r="E70" s="3">
-        <v>4921700</v>
+        <v>4853500</v>
       </c>
       <c r="F70" s="3">
-        <v>4715500</v>
+        <v>4650200</v>
       </c>
       <c r="G70" s="3">
-        <v>2824400</v>
+        <v>2785300</v>
       </c>
       <c r="H70" s="3">
-        <v>2824400</v>
+        <v>2785300</v>
       </c>
       <c r="I70" s="3">
-        <v>2824400</v>
+        <v>2785300</v>
       </c>
       <c r="J70" s="3">
-        <v>2643400</v>
+        <v>2606800</v>
       </c>
       <c r="K70" s="3">
         <v>2600500</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3561200</v>
+        <v>3511900</v>
       </c>
       <c r="E72" s="3">
-        <v>2916800</v>
+        <v>2876400</v>
       </c>
       <c r="F72" s="3">
-        <v>17360400</v>
+        <v>17120000</v>
       </c>
       <c r="G72" s="3">
-        <v>13957300</v>
+        <v>13764100</v>
       </c>
       <c r="H72" s="3">
-        <v>11445500</v>
+        <v>11287000</v>
       </c>
       <c r="I72" s="3">
-        <v>9388100</v>
+        <v>9258200</v>
       </c>
       <c r="J72" s="3">
-        <v>7451200</v>
+        <v>7348100</v>
       </c>
       <c r="K72" s="3">
         <v>7094900</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>30029600</v>
+        <v>29613900</v>
       </c>
       <c r="E76" s="3">
-        <v>29662300</v>
+        <v>29251700</v>
       </c>
       <c r="F76" s="3">
-        <v>37536300</v>
+        <v>37016700</v>
       </c>
       <c r="G76" s="3">
-        <v>35271300</v>
+        <v>34783000</v>
       </c>
       <c r="H76" s="3">
-        <v>33308500</v>
+        <v>32847400</v>
       </c>
       <c r="I76" s="3">
-        <v>31212000</v>
+        <v>30779900</v>
       </c>
       <c r="J76" s="3">
-        <v>27828100</v>
+        <v>27442900</v>
       </c>
       <c r="K76" s="3">
         <v>27992100</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>3547200</v>
+        <v>3498000</v>
       </c>
       <c r="E81" s="3">
-        <v>-1620600</v>
+        <v>-1598200</v>
       </c>
       <c r="F81" s="3">
-        <v>5091600</v>
+        <v>5021200</v>
       </c>
       <c r="G81" s="3">
-        <v>4212200</v>
+        <v>4153900</v>
       </c>
       <c r="H81" s="3">
-        <v>4012700</v>
+        <v>3957200</v>
       </c>
       <c r="I81" s="3">
-        <v>3423000</v>
+        <v>3375600</v>
       </c>
       <c r="J81" s="3">
-        <v>1437300</v>
+        <v>1417400</v>
       </c>
       <c r="K81" s="3">
         <v>2032700</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>429400</v>
+        <v>423400</v>
       </c>
       <c r="E83" s="3">
-        <v>383500</v>
+        <v>378200</v>
       </c>
       <c r="F83" s="3">
-        <v>390900</v>
+        <v>385500</v>
       </c>
       <c r="G83" s="3">
-        <v>484800</v>
+        <v>478100</v>
       </c>
       <c r="H83" s="3">
-        <v>462600</v>
+        <v>456200</v>
       </c>
       <c r="I83" s="3">
-        <v>552000</v>
+        <v>544400</v>
       </c>
       <c r="J83" s="3">
-        <v>413800</v>
+        <v>408100</v>
       </c>
       <c r="K83" s="3">
         <v>503800</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>15092400</v>
+        <v>14883500</v>
       </c>
       <c r="E89" s="3">
-        <v>12287900</v>
+        <v>12117800</v>
       </c>
       <c r="F89" s="3">
-        <v>17111300</v>
+        <v>16874400</v>
       </c>
       <c r="G89" s="3">
-        <v>14815300</v>
+        <v>14610200</v>
       </c>
       <c r="H89" s="3">
-        <v>15180300</v>
+        <v>14970200</v>
       </c>
       <c r="I89" s="3">
-        <v>14179700</v>
+        <v>13983400</v>
       </c>
       <c r="J89" s="3">
-        <v>13147400</v>
+        <v>12965400</v>
       </c>
       <c r="K89" s="3">
         <v>12385300</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-10138900</v>
+        <v>-9998600</v>
       </c>
       <c r="E94" s="3">
-        <v>-13597400</v>
+        <v>-13409200</v>
       </c>
       <c r="F94" s="3">
-        <v>-18062400</v>
+        <v>-17812400</v>
       </c>
       <c r="G94" s="3">
-        <v>-10455200</v>
+        <v>-10310500</v>
       </c>
       <c r="H94" s="3">
-        <v>-10220200</v>
+        <v>-10078800</v>
       </c>
       <c r="I94" s="3">
-        <v>-14042300</v>
+        <v>-13847900</v>
       </c>
       <c r="J94" s="3">
-        <v>-12035900</v>
+        <v>-11869300</v>
       </c>
       <c r="K94" s="3">
         <v>-16531500</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2196300</v>
+        <v>-2165900</v>
       </c>
       <c r="E96" s="3">
-        <v>-2059600</v>
+        <v>-2031100</v>
       </c>
       <c r="F96" s="3">
-        <v>-1847500</v>
+        <v>-1821900</v>
       </c>
       <c r="G96" s="3">
-        <v>-1729200</v>
+        <v>-1705300</v>
       </c>
       <c r="H96" s="3">
-        <v>-1033100</v>
+        <v>-1018800</v>
       </c>
       <c r="I96" s="3">
-        <v>-1321300</v>
+        <v>-1303000</v>
       </c>
       <c r="J96" s="3">
-        <v>-1315400</v>
+        <v>-1297200</v>
       </c>
       <c r="K96" s="3">
         <v>-1158100</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-3726000</v>
+        <v>-3674400</v>
       </c>
       <c r="E100" s="3">
-        <v>-1557800</v>
+        <v>-1536200</v>
       </c>
       <c r="F100" s="3">
-        <v>-1512700</v>
+        <v>-1491800</v>
       </c>
       <c r="G100" s="3">
-        <v>490000</v>
+        <v>483200</v>
       </c>
       <c r="H100" s="3">
-        <v>-1537100</v>
+        <v>-1515800</v>
       </c>
       <c r="I100" s="3">
-        <v>-535000</v>
+        <v>-527600</v>
       </c>
       <c r="J100" s="3">
-        <v>10300</v>
+        <v>10200</v>
       </c>
       <c r="K100" s="3">
         <v>2389000</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-304500</v>
+        <v>-300200</v>
       </c>
       <c r="E101" s="3">
-        <v>432300</v>
+        <v>426300</v>
       </c>
       <c r="F101" s="3">
-        <v>-235700</v>
+        <v>-232500</v>
       </c>
       <c r="G101" s="3">
-        <v>-390200</v>
+        <v>-384800</v>
       </c>
       <c r="H101" s="3">
-        <v>-344400</v>
+        <v>-339600</v>
       </c>
       <c r="I101" s="3">
-        <v>607400</v>
+        <v>599000</v>
       </c>
       <c r="J101" s="3">
-        <v>-486300</v>
+        <v>-479500</v>
       </c>
       <c r="K101" s="3">
         <v>-252300</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>923000</v>
+        <v>910200</v>
       </c>
       <c r="E102" s="3">
-        <v>-2435000</v>
+        <v>-2401300</v>
       </c>
       <c r="F102" s="3">
-        <v>-2699500</v>
+        <v>-2662200</v>
       </c>
       <c r="G102" s="3">
-        <v>4459800</v>
+        <v>4398100</v>
       </c>
       <c r="H102" s="3">
-        <v>3078600</v>
+        <v>3036000</v>
       </c>
       <c r="I102" s="3">
-        <v>209900</v>
+        <v>207000</v>
       </c>
       <c r="J102" s="3">
-        <v>635500</v>
+        <v>626700</v>
       </c>
       <c r="K102" s="3">
         <v>-2009500</v>

--- a/AAII_Financials/Yearly/MFC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MFC_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>24412000</v>
+        <v>24658200</v>
       </c>
       <c r="E8" s="3">
-        <v>16550900</v>
+        <v>16717800</v>
       </c>
       <c r="F8" s="3">
-        <v>40758800</v>
+        <v>41169900</v>
       </c>
       <c r="G8" s="3">
-        <v>54196400</v>
+        <v>54743000</v>
       </c>
       <c r="H8" s="3">
-        <v>56713600</v>
+        <v>57285600</v>
       </c>
       <c r="I8" s="3">
-        <v>27156500</v>
+        <v>27430400</v>
       </c>
       <c r="J8" s="3">
-        <v>42503500</v>
+        <v>42932100</v>
       </c>
       <c r="K8" s="3">
         <v>38776500</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>14124800</v>
+        <v>14267300</v>
       </c>
       <c r="E9" s="3">
-        <v>10943800</v>
+        <v>11054200</v>
       </c>
       <c r="F9" s="3">
-        <v>30028600</v>
+        <v>30331400</v>
       </c>
       <c r="G9" s="3">
-        <v>43628700</v>
+        <v>44068700</v>
       </c>
       <c r="H9" s="3">
-        <v>44281600</v>
+        <v>44728300</v>
       </c>
       <c r="I9" s="3">
-        <v>14792400</v>
+        <v>14941600</v>
       </c>
       <c r="J9" s="3">
-        <v>32307400</v>
+        <v>32633200</v>
       </c>
       <c r="K9" s="3">
         <v>28237800</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>10287200</v>
+        <v>10390900</v>
       </c>
       <c r="E10" s="3">
-        <v>5607100</v>
+        <v>5663600</v>
       </c>
       <c r="F10" s="3">
-        <v>10730300</v>
+        <v>10838500</v>
       </c>
       <c r="G10" s="3">
-        <v>10567700</v>
+        <v>10674300</v>
       </c>
       <c r="H10" s="3">
-        <v>12431900</v>
+        <v>12557300</v>
       </c>
       <c r="I10" s="3">
-        <v>12364100</v>
+        <v>12488800</v>
       </c>
       <c r="J10" s="3">
-        <v>10196100</v>
+        <v>10298900</v>
       </c>
       <c r="K10" s="3">
         <v>10538700</v>
@@ -973,13 +973,13 @@
         <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>110000</v>
+        <v>111200</v>
       </c>
       <c r="F14" s="3">
-        <v>-10900</v>
+        <v>-11000</v>
       </c>
       <c r="G14" s="3">
-        <v>512300</v>
+        <v>517500</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>19710000</v>
+        <v>19908800</v>
       </c>
       <c r="E17" s="3">
-        <v>18837700</v>
+        <v>19027700</v>
       </c>
       <c r="F17" s="3">
-        <v>34100900</v>
+        <v>34444800</v>
       </c>
       <c r="G17" s="3">
-        <v>48401300</v>
+        <v>48889500</v>
       </c>
       <c r="H17" s="3">
-        <v>51219400</v>
+        <v>51736000</v>
       </c>
       <c r="I17" s="3">
-        <v>22205300</v>
+        <v>22429300</v>
       </c>
       <c r="J17" s="3">
-        <v>39850800</v>
+        <v>40252700</v>
       </c>
       <c r="K17" s="3">
         <v>35619900</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4702000</v>
+        <v>4749400</v>
       </c>
       <c r="E18" s="3">
-        <v>-2286800</v>
+        <v>-2309900</v>
       </c>
       <c r="F18" s="3">
-        <v>6658000</v>
+        <v>6725100</v>
       </c>
       <c r="G18" s="3">
-        <v>5795100</v>
+        <v>5853500</v>
       </c>
       <c r="H18" s="3">
-        <v>5494100</v>
+        <v>5549500</v>
       </c>
       <c r="I18" s="3">
-        <v>4951200</v>
+        <v>5001100</v>
       </c>
       <c r="J18" s="3">
-        <v>2652700</v>
+        <v>2679400</v>
       </c>
       <c r="K18" s="3">
         <v>3156700</v>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>983800</v>
+        <v>993700</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5124300</v>
+        <v>5177200</v>
       </c>
       <c r="E21" s="3">
-        <v>-925800</v>
+        <v>-934000</v>
       </c>
       <c r="F21" s="3">
-        <v>7042500</v>
+        <v>7114600</v>
       </c>
       <c r="G21" s="3">
-        <v>6271900</v>
+        <v>6336600</v>
       </c>
       <c r="H21" s="3">
-        <v>5949200</v>
+        <v>6010500</v>
       </c>
       <c r="I21" s="3">
-        <v>5494200</v>
+        <v>5551200</v>
       </c>
       <c r="J21" s="3">
-        <v>3059800</v>
+        <v>3091800</v>
       </c>
       <c r="K21" s="3">
         <v>3663300</v>
@@ -1278,22 +1278,22 @@
         <v>8</v>
       </c>
       <c r="E22" s="3">
-        <v>983800</v>
+        <v>993700</v>
       </c>
       <c r="F22" s="3">
-        <v>736800</v>
+        <v>744200</v>
       </c>
       <c r="G22" s="3">
-        <v>860700</v>
+        <v>869300</v>
       </c>
       <c r="H22" s="3">
-        <v>961200</v>
+        <v>970900</v>
       </c>
       <c r="I22" s="3">
-        <v>929200</v>
+        <v>938500</v>
       </c>
       <c r="J22" s="3">
-        <v>830100</v>
+        <v>838400</v>
       </c>
       <c r="K22" s="3">
         <v>736500</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4702000</v>
+        <v>4749400</v>
       </c>
       <c r="E23" s="3">
-        <v>-2286800</v>
+        <v>-2309900</v>
       </c>
       <c r="F23" s="3">
-        <v>5921200</v>
+        <v>5980900</v>
       </c>
       <c r="G23" s="3">
-        <v>4934400</v>
+        <v>4984200</v>
       </c>
       <c r="H23" s="3">
-        <v>4532900</v>
+        <v>4578600</v>
       </c>
       <c r="I23" s="3">
-        <v>4022000</v>
+        <v>4062600</v>
       </c>
       <c r="J23" s="3">
-        <v>1822600</v>
+        <v>1841000</v>
       </c>
       <c r="K23" s="3">
         <v>2420200</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>615800</v>
+        <v>622000</v>
       </c>
       <c r="E24" s="3">
-        <v>-844600</v>
+        <v>-853200</v>
       </c>
       <c r="F24" s="3">
-        <v>884000</v>
+        <v>892900</v>
       </c>
       <c r="G24" s="3">
-        <v>870900</v>
+        <v>879700</v>
       </c>
       <c r="H24" s="3">
-        <v>523200</v>
+        <v>528500</v>
       </c>
       <c r="I24" s="3">
-        <v>693800</v>
+        <v>700800</v>
       </c>
       <c r="J24" s="3">
-        <v>174200</v>
+        <v>175900</v>
       </c>
       <c r="K24" s="3">
         <v>142500</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4086200</v>
+        <v>4127400</v>
       </c>
       <c r="E26" s="3">
-        <v>-1442200</v>
+        <v>-1456800</v>
       </c>
       <c r="F26" s="3">
-        <v>5037200</v>
+        <v>5088000</v>
       </c>
       <c r="G26" s="3">
-        <v>4063600</v>
+        <v>4104500</v>
       </c>
       <c r="H26" s="3">
-        <v>4009600</v>
+        <v>4050100</v>
       </c>
       <c r="I26" s="3">
-        <v>3328200</v>
+        <v>3361800</v>
       </c>
       <c r="J26" s="3">
-        <v>1648500</v>
+        <v>1665100</v>
       </c>
       <c r="K26" s="3">
         <v>2277700</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>3498000</v>
+        <v>3533300</v>
       </c>
       <c r="E27" s="3">
-        <v>-1598200</v>
+        <v>-1614300</v>
       </c>
       <c r="F27" s="3">
-        <v>5021200</v>
+        <v>5071800</v>
       </c>
       <c r="G27" s="3">
-        <v>4153900</v>
+        <v>4195800</v>
       </c>
       <c r="H27" s="3">
-        <v>3957200</v>
+        <v>3997100</v>
       </c>
       <c r="I27" s="3">
-        <v>3142400</v>
+        <v>3174100</v>
       </c>
       <c r="J27" s="3">
-        <v>1417400</v>
+        <v>1431700</v>
       </c>
       <c r="K27" s="3">
         <v>2032700</v>
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>233200</v>
+        <v>235600</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>8</v>
@@ -1728,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-983800</v>
+        <v>-993700</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>3498000</v>
+        <v>3533300</v>
       </c>
       <c r="E33" s="3">
-        <v>-1598200</v>
+        <v>-1614300</v>
       </c>
       <c r="F33" s="3">
-        <v>5021200</v>
+        <v>5071800</v>
       </c>
       <c r="G33" s="3">
-        <v>4153900</v>
+        <v>4195800</v>
       </c>
       <c r="H33" s="3">
-        <v>3957200</v>
+        <v>3997100</v>
       </c>
       <c r="I33" s="3">
-        <v>3375600</v>
+        <v>3409700</v>
       </c>
       <c r="J33" s="3">
-        <v>1417400</v>
+        <v>1431700</v>
       </c>
       <c r="K33" s="3">
         <v>2032700</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>3498000</v>
+        <v>3533300</v>
       </c>
       <c r="E35" s="3">
-        <v>-1598200</v>
+        <v>-1614300</v>
       </c>
       <c r="F35" s="3">
-        <v>5021200</v>
+        <v>5071800</v>
       </c>
       <c r="G35" s="3">
-        <v>4153900</v>
+        <v>4195800</v>
       </c>
       <c r="H35" s="3">
-        <v>3957200</v>
+        <v>3997100</v>
       </c>
       <c r="I35" s="3">
-        <v>3375600</v>
+        <v>3409700</v>
       </c>
       <c r="J35" s="3">
-        <v>1417400</v>
+        <v>1431700</v>
       </c>
       <c r="K35" s="3">
         <v>2032700</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>14821500</v>
+        <v>14971000</v>
       </c>
       <c r="E41" s="3">
-        <v>13957900</v>
+        <v>14098700</v>
       </c>
       <c r="F41" s="3">
-        <v>16465600</v>
+        <v>16631700</v>
       </c>
       <c r="G41" s="3">
-        <v>19069500</v>
+        <v>19261800</v>
       </c>
       <c r="H41" s="3">
-        <v>14793800</v>
+        <v>14943000</v>
       </c>
       <c r="I41" s="3">
-        <v>11816800</v>
+        <v>11936000</v>
       </c>
       <c r="J41" s="3">
-        <v>11634700</v>
+        <v>11752000</v>
       </c>
       <c r="K41" s="3">
         <v>11014900</v>
@@ -2086,16 +2086,16 @@
         <v>8</v>
       </c>
       <c r="E43" s="3">
-        <v>1055200</v>
+        <v>1065900</v>
       </c>
       <c r="F43" s="3">
-        <v>943000</v>
+        <v>952500</v>
       </c>
       <c r="G43" s="3">
-        <v>1052300</v>
+        <v>1062900</v>
       </c>
       <c r="H43" s="3">
-        <v>1009300</v>
+        <v>1019500</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>8</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>289330000</v>
+        <v>292248000</v>
       </c>
       <c r="E47" s="3">
-        <v>283164000</v>
+        <v>286020000</v>
       </c>
       <c r="F47" s="3">
-        <v>294786000</v>
+        <v>297759000</v>
       </c>
       <c r="G47" s="3">
-        <v>280434000</v>
+        <v>283263000</v>
       </c>
       <c r="H47" s="3">
-        <v>261062000</v>
+        <v>263695000</v>
       </c>
       <c r="I47" s="3">
-        <v>245919000</v>
+        <v>248400000</v>
       </c>
       <c r="J47" s="3">
-        <v>231933000</v>
+        <v>234272000</v>
       </c>
       <c r="K47" s="3">
         <v>222987000</v>
@@ -2320,7 +2320,7 @@
         <v>8</v>
       </c>
       <c r="H48" s="3">
-        <v>277700</v>
+        <v>280500</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>8</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7513500</v>
+        <v>7589300</v>
       </c>
       <c r="E49" s="3">
-        <v>15331700</v>
+        <v>15486300</v>
       </c>
       <c r="F49" s="3">
-        <v>7225700</v>
+        <v>7298500</v>
       </c>
       <c r="G49" s="3">
-        <v>7235900</v>
+        <v>7308800</v>
       </c>
       <c r="H49" s="3">
-        <v>7269400</v>
+        <v>7342700</v>
       </c>
       <c r="I49" s="3">
-        <v>7358300</v>
+        <v>7432500</v>
       </c>
       <c r="J49" s="3">
-        <v>7171000</v>
+        <v>7243300</v>
       </c>
       <c r="K49" s="3">
         <v>7347900</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4911100</v>
+        <v>4960600</v>
       </c>
       <c r="E52" s="3">
-        <v>4888500</v>
+        <v>4937800</v>
       </c>
       <c r="F52" s="3">
-        <v>3828900</v>
+        <v>3867500</v>
       </c>
       <c r="G52" s="3">
-        <v>3528700</v>
+        <v>3564200</v>
       </c>
       <c r="H52" s="3">
-        <v>3333300</v>
+        <v>3367000</v>
       </c>
       <c r="I52" s="3">
-        <v>3146800</v>
+        <v>3178500</v>
       </c>
       <c r="J52" s="3">
-        <v>3329700</v>
+        <v>3363300</v>
       </c>
       <c r="K52" s="3">
         <v>3227200</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>638083000</v>
+        <v>644519000</v>
       </c>
       <c r="E54" s="3">
-        <v>607559000</v>
+        <v>613687000</v>
       </c>
       <c r="F54" s="3">
-        <v>668742000</v>
+        <v>675486000</v>
       </c>
       <c r="G54" s="3">
-        <v>641563000</v>
+        <v>648034000</v>
       </c>
       <c r="H54" s="3">
-        <v>589662000</v>
+        <v>595609000</v>
       </c>
       <c r="I54" s="3">
-        <v>546768000</v>
+        <v>552282000</v>
       </c>
       <c r="J54" s="3">
-        <v>531655000</v>
+        <v>537017000</v>
       </c>
       <c r="K54" s="3">
         <v>523942000</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>569747000</v>
+        <v>575493000</v>
       </c>
       <c r="E59" s="3">
-        <v>802073000</v>
+        <v>810163000</v>
       </c>
       <c r="F59" s="3">
-        <v>317564000</v>
+        <v>320767000</v>
       </c>
       <c r="G59" s="3">
-        <v>293763000</v>
+        <v>296726000</v>
       </c>
       <c r="H59" s="3">
-        <v>275818000</v>
+        <v>278600000</v>
       </c>
       <c r="I59" s="3">
-        <v>252644000</v>
+        <v>255192000</v>
       </c>
       <c r="J59" s="3">
-        <v>258729000</v>
+        <v>261338000</v>
       </c>
       <c r="K59" s="3">
         <v>251392000</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>9282900</v>
+        <v>9376600</v>
       </c>
       <c r="E61" s="3">
-        <v>9004600</v>
+        <v>9095400</v>
       </c>
       <c r="F61" s="3">
-        <v>8644600</v>
+        <v>8731700</v>
       </c>
       <c r="G61" s="3">
-        <v>10197500</v>
+        <v>10300400</v>
       </c>
       <c r="H61" s="3">
-        <v>8798300</v>
+        <v>8887100</v>
       </c>
       <c r="I61" s="3">
-        <v>9839000</v>
+        <v>9938200</v>
       </c>
       <c r="J61" s="3">
-        <v>9599200</v>
+        <v>9696000</v>
       </c>
       <c r="K61" s="3">
         <v>9361000</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1236700</v>
+        <v>1249200</v>
       </c>
       <c r="E62" s="3">
-        <v>1119400</v>
+        <v>1130700</v>
       </c>
       <c r="F62" s="3">
-        <v>2017900</v>
+        <v>2038300</v>
       </c>
       <c r="G62" s="3">
-        <v>1905000</v>
+        <v>1924200</v>
       </c>
       <c r="H62" s="3">
-        <v>1437100</v>
+        <v>1451600</v>
       </c>
       <c r="I62" s="3">
-        <v>1322000</v>
+        <v>1335300</v>
       </c>
       <c r="J62" s="3">
-        <v>933500</v>
+        <v>943000</v>
       </c>
       <c r="K62" s="3">
         <v>988000</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>603616000</v>
+        <v>609704000</v>
       </c>
       <c r="E66" s="3">
-        <v>573454000</v>
+        <v>579238000</v>
       </c>
       <c r="F66" s="3">
-        <v>627075000</v>
+        <v>633399000</v>
       </c>
       <c r="G66" s="3">
-        <v>603995000</v>
+        <v>610087000</v>
       </c>
       <c r="H66" s="3">
-        <v>554029000</v>
+        <v>559617000</v>
       </c>
       <c r="I66" s="3">
-        <v>513202000</v>
+        <v>518378000</v>
       </c>
       <c r="J66" s="3">
-        <v>501605000</v>
+        <v>506664000</v>
       </c>
       <c r="K66" s="3">
         <v>493350000</v>
@@ -3220,25 +3220,25 @@
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>4853500</v>
+        <v>4902500</v>
       </c>
       <c r="E70" s="3">
-        <v>4853500</v>
+        <v>4902500</v>
       </c>
       <c r="F70" s="3">
-        <v>4650200</v>
+        <v>4697100</v>
       </c>
       <c r="G70" s="3">
-        <v>2785300</v>
+        <v>2813400</v>
       </c>
       <c r="H70" s="3">
-        <v>2785300</v>
+        <v>2813400</v>
       </c>
       <c r="I70" s="3">
-        <v>2785300</v>
+        <v>2813400</v>
       </c>
       <c r="J70" s="3">
-        <v>2606800</v>
+        <v>2633100</v>
       </c>
       <c r="K70" s="3">
         <v>2600500</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3511900</v>
+        <v>3547300</v>
       </c>
       <c r="E72" s="3">
-        <v>2876400</v>
+        <v>2905400</v>
       </c>
       <c r="F72" s="3">
-        <v>17120000</v>
+        <v>17292700</v>
       </c>
       <c r="G72" s="3">
-        <v>13764100</v>
+        <v>13902900</v>
       </c>
       <c r="H72" s="3">
-        <v>11287000</v>
+        <v>11400900</v>
       </c>
       <c r="I72" s="3">
-        <v>9258200</v>
+        <v>9351500</v>
       </c>
       <c r="J72" s="3">
-        <v>7348100</v>
+        <v>7422200</v>
       </c>
       <c r="K72" s="3">
         <v>7094900</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>29613900</v>
+        <v>29912600</v>
       </c>
       <c r="E76" s="3">
-        <v>29251700</v>
+        <v>29546700</v>
       </c>
       <c r="F76" s="3">
-        <v>37016700</v>
+        <v>37390000</v>
       </c>
       <c r="G76" s="3">
-        <v>34783000</v>
+        <v>35133800</v>
       </c>
       <c r="H76" s="3">
-        <v>32847400</v>
+        <v>33178700</v>
       </c>
       <c r="I76" s="3">
-        <v>30779900</v>
+        <v>31090400</v>
       </c>
       <c r="J76" s="3">
-        <v>27442900</v>
+        <v>27719700</v>
       </c>
       <c r="K76" s="3">
         <v>27992100</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>3498000</v>
+        <v>3533300</v>
       </c>
       <c r="E81" s="3">
-        <v>-1598200</v>
+        <v>-1614300</v>
       </c>
       <c r="F81" s="3">
-        <v>5021200</v>
+        <v>5071800</v>
       </c>
       <c r="G81" s="3">
-        <v>4153900</v>
+        <v>4195800</v>
       </c>
       <c r="H81" s="3">
-        <v>3957200</v>
+        <v>3997100</v>
       </c>
       <c r="I81" s="3">
-        <v>3375600</v>
+        <v>3409700</v>
       </c>
       <c r="J81" s="3">
-        <v>1417400</v>
+        <v>1431700</v>
       </c>
       <c r="K81" s="3">
         <v>2032700</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>423400</v>
+        <v>427700</v>
       </c>
       <c r="E83" s="3">
-        <v>378200</v>
+        <v>382000</v>
       </c>
       <c r="F83" s="3">
-        <v>385500</v>
+        <v>389400</v>
       </c>
       <c r="G83" s="3">
-        <v>478100</v>
+        <v>482900</v>
       </c>
       <c r="H83" s="3">
-        <v>456200</v>
+        <v>460800</v>
       </c>
       <c r="I83" s="3">
-        <v>544400</v>
+        <v>549900</v>
       </c>
       <c r="J83" s="3">
-        <v>408100</v>
+        <v>412200</v>
       </c>
       <c r="K83" s="3">
         <v>503800</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>14883500</v>
+        <v>15033600</v>
       </c>
       <c r="E89" s="3">
-        <v>12117800</v>
+        <v>12240000</v>
       </c>
       <c r="F89" s="3">
-        <v>16874400</v>
+        <v>17044600</v>
       </c>
       <c r="G89" s="3">
-        <v>14610200</v>
+        <v>14757500</v>
       </c>
       <c r="H89" s="3">
-        <v>14970200</v>
+        <v>15121200</v>
       </c>
       <c r="I89" s="3">
-        <v>13983400</v>
+        <v>14124500</v>
       </c>
       <c r="J89" s="3">
-        <v>12965400</v>
+        <v>13096100</v>
       </c>
       <c r="K89" s="3">
         <v>12385300</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-9998600</v>
+        <v>-10099400</v>
       </c>
       <c r="E94" s="3">
-        <v>-13409200</v>
+        <v>-13544400</v>
       </c>
       <c r="F94" s="3">
-        <v>-17812400</v>
+        <v>-17992000</v>
       </c>
       <c r="G94" s="3">
-        <v>-10310500</v>
+        <v>-10414500</v>
       </c>
       <c r="H94" s="3">
-        <v>-10078800</v>
+        <v>-10180400</v>
       </c>
       <c r="I94" s="3">
-        <v>-13847900</v>
+        <v>-13987600</v>
       </c>
       <c r="J94" s="3">
-        <v>-11869300</v>
+        <v>-11989000</v>
       </c>
       <c r="K94" s="3">
         <v>-16531500</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2165900</v>
+        <v>-2187700</v>
       </c>
       <c r="E96" s="3">
-        <v>-2031100</v>
+        <v>-2051500</v>
       </c>
       <c r="F96" s="3">
-        <v>-1821900</v>
+        <v>-1840300</v>
       </c>
       <c r="G96" s="3">
-        <v>-1705300</v>
+        <v>-1722500</v>
       </c>
       <c r="H96" s="3">
-        <v>-1018800</v>
+        <v>-1029100</v>
       </c>
       <c r="I96" s="3">
-        <v>-1303000</v>
+        <v>-1316200</v>
       </c>
       <c r="J96" s="3">
-        <v>-1297200</v>
+        <v>-1310300</v>
       </c>
       <c r="K96" s="3">
         <v>-1158100</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-3674400</v>
+        <v>-3711500</v>
       </c>
       <c r="E100" s="3">
-        <v>-1536200</v>
+        <v>-1551700</v>
       </c>
       <c r="F100" s="3">
-        <v>-1491800</v>
+        <v>-1506800</v>
       </c>
       <c r="G100" s="3">
-        <v>483200</v>
+        <v>488000</v>
       </c>
       <c r="H100" s="3">
-        <v>-1515800</v>
+        <v>-1531100</v>
       </c>
       <c r="I100" s="3">
-        <v>-527600</v>
+        <v>-532900</v>
       </c>
       <c r="J100" s="3">
-        <v>10200</v>
+        <v>10300</v>
       </c>
       <c r="K100" s="3">
         <v>2389000</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-300200</v>
+        <v>-303300</v>
       </c>
       <c r="E101" s="3">
-        <v>426300</v>
+        <v>430600</v>
       </c>
       <c r="F101" s="3">
-        <v>-232500</v>
+        <v>-234800</v>
       </c>
       <c r="G101" s="3">
-        <v>-384800</v>
+        <v>-388700</v>
       </c>
       <c r="H101" s="3">
-        <v>-339600</v>
+        <v>-343000</v>
       </c>
       <c r="I101" s="3">
-        <v>599000</v>
+        <v>605100</v>
       </c>
       <c r="J101" s="3">
-        <v>-479500</v>
+        <v>-484400</v>
       </c>
       <c r="K101" s="3">
         <v>-252300</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>910200</v>
+        <v>919400</v>
       </c>
       <c r="E102" s="3">
-        <v>-2401300</v>
+        <v>-2425500</v>
       </c>
       <c r="F102" s="3">
-        <v>-2662200</v>
+        <v>-2689000</v>
       </c>
       <c r="G102" s="3">
-        <v>4398100</v>
+        <v>4442400</v>
       </c>
       <c r="H102" s="3">
-        <v>3036000</v>
+        <v>3066600</v>
       </c>
       <c r="I102" s="3">
-        <v>207000</v>
+        <v>209100</v>
       </c>
       <c r="J102" s="3">
-        <v>626700</v>
+        <v>633100</v>
       </c>
       <c r="K102" s="3">
         <v>-2009500</v>

--- a/AAII_Financials/Yearly/MFC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MFC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
   <si>
     <t>MFC</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>24658200</v>
+        <v>20631100</v>
       </c>
       <c r="E8" s="3">
-        <v>16717800</v>
+        <v>12495000</v>
       </c>
       <c r="F8" s="3">
-        <v>41169900</v>
+        <v>47286800</v>
       </c>
       <c r="G8" s="3">
-        <v>54743000</v>
+        <v>60525000</v>
       </c>
       <c r="H8" s="3">
-        <v>57285600</v>
+        <v>59999900</v>
       </c>
       <c r="I8" s="3">
-        <v>27430400</v>
+        <v>27308800</v>
       </c>
       <c r="J8" s="3">
-        <v>42932100</v>
+        <v>45228400</v>
       </c>
       <c r="K8" s="3">
         <v>38776500</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>14267300</v>
+        <v>10261800</v>
       </c>
       <c r="E9" s="3">
-        <v>11054200</v>
+        <v>9844700</v>
       </c>
       <c r="F9" s="3">
-        <v>30331400</v>
+        <v>32956400</v>
       </c>
       <c r="G9" s="3">
-        <v>44068700</v>
+        <v>52221800</v>
       </c>
       <c r="H9" s="3">
-        <v>44728300</v>
+        <v>48940100</v>
       </c>
       <c r="I9" s="3">
-        <v>14941600</v>
+        <v>23333900</v>
       </c>
       <c r="J9" s="3">
-        <v>32633200</v>
+        <v>34461900</v>
       </c>
       <c r="K9" s="3">
         <v>28237800</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>10390900</v>
+        <v>10369300</v>
       </c>
       <c r="E10" s="3">
-        <v>5663600</v>
+        <v>2650300</v>
       </c>
       <c r="F10" s="3">
-        <v>10838500</v>
+        <v>14330400</v>
       </c>
       <c r="G10" s="3">
-        <v>10674300</v>
+        <v>8303200</v>
       </c>
       <c r="H10" s="3">
-        <v>12557300</v>
+        <v>11059800</v>
       </c>
       <c r="I10" s="3">
-        <v>12488800</v>
+        <v>3975000</v>
       </c>
       <c r="J10" s="3">
-        <v>10298900</v>
+        <v>10766500</v>
       </c>
       <c r="K10" s="3">
         <v>10538700</v>
@@ -969,17 +969,17 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>40900</v>
       </c>
       <c r="E14" s="3">
-        <v>111200</v>
+        <v>19200</v>
       </c>
       <c r="F14" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>517500</v>
+        <v>118500</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>229400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>223900</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>301100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>366500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>353100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>439700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>350100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>19908800</v>
+        <v>14527900</v>
       </c>
       <c r="E17" s="3">
-        <v>19027700</v>
+        <v>14017800</v>
       </c>
       <c r="F17" s="3">
-        <v>34444800</v>
+        <v>39949000</v>
       </c>
       <c r="G17" s="3">
-        <v>48889500</v>
+        <v>54284300</v>
       </c>
       <c r="H17" s="3">
-        <v>51736000</v>
+        <v>54187400</v>
       </c>
       <c r="I17" s="3">
-        <v>22429300</v>
+        <v>22329900</v>
       </c>
       <c r="J17" s="3">
-        <v>40252700</v>
+        <v>42325800</v>
       </c>
       <c r="K17" s="3">
         <v>35619900</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4749400</v>
+        <v>6103100</v>
       </c>
       <c r="E18" s="3">
-        <v>-2309900</v>
+        <v>-1522800</v>
       </c>
       <c r="F18" s="3">
-        <v>6725100</v>
+        <v>7337900</v>
       </c>
       <c r="G18" s="3">
-        <v>5853500</v>
+        <v>6240800</v>
       </c>
       <c r="H18" s="3">
-        <v>5549500</v>
+        <v>5812500</v>
       </c>
       <c r="I18" s="3">
-        <v>5001100</v>
+        <v>4979000</v>
       </c>
       <c r="J18" s="3">
-        <v>2679400</v>
+        <v>2902500</v>
       </c>
       <c r="K18" s="3">
         <v>3156700</v>
@@ -1184,26 +1184,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>993700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5177200</v>
+        <v>6332600</v>
       </c>
       <c r="E21" s="3">
-        <v>-934000</v>
+        <v>-1298900</v>
       </c>
       <c r="F21" s="3">
-        <v>7114600</v>
+        <v>7638900</v>
       </c>
       <c r="G21" s="3">
-        <v>6336600</v>
+        <v>6607300</v>
       </c>
       <c r="H21" s="3">
-        <v>6010500</v>
+        <v>6165600</v>
       </c>
       <c r="I21" s="3">
-        <v>5551200</v>
+        <v>5418700</v>
       </c>
       <c r="J21" s="3">
-        <v>3091800</v>
+        <v>3252600</v>
       </c>
       <c r="K21" s="3">
         <v>3663300</v>
@@ -1274,26 +1274,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>1176700</v>
       </c>
       <c r="E22" s="3">
-        <v>993700</v>
+        <v>776600</v>
       </c>
       <c r="F22" s="3">
-        <v>744200</v>
+        <v>798900</v>
       </c>
       <c r="G22" s="3">
-        <v>869300</v>
+        <v>926900</v>
       </c>
       <c r="H22" s="3">
-        <v>970900</v>
+        <v>1016900</v>
       </c>
       <c r="I22" s="3">
-        <v>938500</v>
+        <v>934400</v>
       </c>
       <c r="J22" s="3">
-        <v>838400</v>
+        <v>908200</v>
       </c>
       <c r="K22" s="3">
         <v>736500</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4749400</v>
+        <v>4885500</v>
       </c>
       <c r="E23" s="3">
-        <v>-2309900</v>
+        <v>-2318600</v>
       </c>
       <c r="F23" s="3">
-        <v>5980900</v>
+        <v>6420400</v>
       </c>
       <c r="G23" s="3">
-        <v>4984200</v>
+        <v>5313900</v>
       </c>
       <c r="H23" s="3">
-        <v>4578600</v>
+        <v>4795600</v>
       </c>
       <c r="I23" s="3">
-        <v>4062600</v>
+        <v>4044600</v>
       </c>
       <c r="J23" s="3">
-        <v>1841000</v>
+        <v>1994300</v>
       </c>
       <c r="K23" s="3">
         <v>2420200</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>622000</v>
+        <v>639800</v>
       </c>
       <c r="E24" s="3">
-        <v>-853200</v>
+        <v>-856300</v>
       </c>
       <c r="F24" s="3">
-        <v>892900</v>
+        <v>958500</v>
       </c>
       <c r="G24" s="3">
-        <v>879700</v>
+        <v>937800</v>
       </c>
       <c r="H24" s="3">
-        <v>528500</v>
+        <v>553600</v>
       </c>
       <c r="I24" s="3">
-        <v>700800</v>
+        <v>463200</v>
       </c>
       <c r="J24" s="3">
-        <v>175900</v>
+        <v>190600</v>
       </c>
       <c r="K24" s="3">
         <v>142500</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4127400</v>
+        <v>4245700</v>
       </c>
       <c r="E26" s="3">
-        <v>-1456800</v>
+        <v>-1462200</v>
       </c>
       <c r="F26" s="3">
-        <v>5088000</v>
+        <v>5461900</v>
       </c>
       <c r="G26" s="3">
-        <v>4104500</v>
+        <v>4376100</v>
       </c>
       <c r="H26" s="3">
-        <v>4050100</v>
+        <v>4242000</v>
       </c>
       <c r="I26" s="3">
-        <v>3361800</v>
+        <v>3581400</v>
       </c>
       <c r="J26" s="3">
-        <v>1665100</v>
+        <v>1803700</v>
       </c>
       <c r="K26" s="3">
         <v>2277700</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>3533300</v>
+        <v>3634600</v>
       </c>
       <c r="E27" s="3">
-        <v>-1614300</v>
+        <v>-1620300</v>
       </c>
       <c r="F27" s="3">
-        <v>5071800</v>
+        <v>5444500</v>
       </c>
       <c r="G27" s="3">
-        <v>4195800</v>
+        <v>4473400</v>
       </c>
       <c r="H27" s="3">
-        <v>3997100</v>
+        <v>4186500</v>
       </c>
       <c r="I27" s="3">
-        <v>3174100</v>
+        <v>3394600</v>
       </c>
       <c r="J27" s="3">
-        <v>1431700</v>
+        <v>1550900</v>
       </c>
       <c r="K27" s="3">
         <v>2032700</v>
@@ -1589,26 +1589,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>235600</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1724,26 +1724,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-993700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>3533300</v>
+        <v>4136700</v>
       </c>
       <c r="E33" s="3">
-        <v>-1614300</v>
+        <v>-1551600</v>
       </c>
       <c r="F33" s="3">
-        <v>5071800</v>
+        <v>5260400</v>
       </c>
       <c r="G33" s="3">
-        <v>4195800</v>
+        <v>4179900</v>
       </c>
       <c r="H33" s="3">
-        <v>3997100</v>
+        <v>4062300</v>
       </c>
       <c r="I33" s="3">
-        <v>3409700</v>
+        <v>3424600</v>
       </c>
       <c r="J33" s="3">
-        <v>1431700</v>
+        <v>1649000</v>
       </c>
       <c r="K33" s="3">
         <v>2032700</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>3533300</v>
+        <v>4136700</v>
       </c>
       <c r="E35" s="3">
-        <v>-1614300</v>
+        <v>-1551600</v>
       </c>
       <c r="F35" s="3">
-        <v>5071800</v>
+        <v>5260400</v>
       </c>
       <c r="G35" s="3">
-        <v>4195800</v>
+        <v>4179900</v>
       </c>
       <c r="H35" s="3">
-        <v>3997100</v>
+        <v>4062300</v>
       </c>
       <c r="I35" s="3">
-        <v>3409700</v>
+        <v>3424600</v>
       </c>
       <c r="J35" s="3">
-        <v>1431700</v>
+        <v>1649000</v>
       </c>
       <c r="K35" s="3">
         <v>2032700</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>14971000</v>
+        <v>15400200</v>
       </c>
       <c r="E41" s="3">
-        <v>14098700</v>
+        <v>14151600</v>
       </c>
       <c r="F41" s="3">
-        <v>16631700</v>
+        <v>17854000</v>
       </c>
       <c r="G41" s="3">
-        <v>19261800</v>
+        <v>20536000</v>
       </c>
       <c r="H41" s="3">
-        <v>14943000</v>
+        <v>15651100</v>
       </c>
       <c r="I41" s="3">
-        <v>11936000</v>
+        <v>11883100</v>
       </c>
       <c r="J41" s="3">
-        <v>11752000</v>
+        <v>12730400</v>
       </c>
       <c r="K41" s="3">
         <v>11014900</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>4401700</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>4373400</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>11830200</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>20197000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>12013600</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>8440900</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>10602200</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2082,26 +2082,26 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>8</v>
+      <c r="D43" s="3">
+        <v>909400</v>
       </c>
       <c r="E43" s="3">
-        <v>1065900</v>
+        <v>1335900</v>
       </c>
       <c r="F43" s="3">
-        <v>952500</v>
+        <v>1544100</v>
       </c>
       <c r="G43" s="3">
-        <v>1062900</v>
+        <v>1133300</v>
       </c>
       <c r="H43" s="3">
-        <v>1019500</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
+        <v>1067800</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1003300</v>
+      </c>
+      <c r="J43" s="3">
+        <v>915400</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>8</v>
@@ -2127,26 +2127,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>36393200</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>37811600</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>39314400</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>39567600</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>36798500</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>34931200</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>27760600</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>57104600</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>57672400</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>70542600</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>81433800</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>65531000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>56258500</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>52008600</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>292248000</v>
+        <v>249097800</v>
       </c>
       <c r="E47" s="3">
-        <v>286020000</v>
+        <v>230655700</v>
       </c>
       <c r="F47" s="3">
-        <v>297759000</v>
+        <v>261048300</v>
       </c>
       <c r="G47" s="3">
-        <v>283263000</v>
+        <v>245955900</v>
       </c>
       <c r="H47" s="3">
-        <v>263695000</v>
+        <v>221822800</v>
       </c>
       <c r="I47" s="3">
-        <v>248400000</v>
+        <v>196454500</v>
       </c>
       <c r="J47" s="3">
-        <v>234272000</v>
+        <v>201071700</v>
       </c>
       <c r="K47" s="3">
         <v>222987000</v>
@@ -2307,26 +2307,26 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>8</v>
+      <c r="D48" s="3">
+        <v>1961900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2107300</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1431900</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1451900</v>
       </c>
       <c r="H48" s="3">
-        <v>280500</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>8</v>
+        <v>1484900</v>
+      </c>
+      <c r="I48" s="3">
+        <v>1477400</v>
+      </c>
+      <c r="J48" s="3">
+        <v>1021500</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>8</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7589300</v>
+        <v>7806900</v>
       </c>
       <c r="E49" s="3">
-        <v>15486300</v>
+        <v>7772200</v>
       </c>
       <c r="F49" s="3">
-        <v>7298500</v>
+        <v>7834900</v>
       </c>
       <c r="G49" s="3">
-        <v>7308800</v>
+        <v>7792300</v>
       </c>
       <c r="H49" s="3">
-        <v>7342700</v>
+        <v>7690600</v>
       </c>
       <c r="I49" s="3">
-        <v>7432500</v>
+        <v>7399600</v>
       </c>
       <c r="J49" s="3">
-        <v>7243300</v>
+        <v>7846400</v>
       </c>
       <c r="K49" s="3">
         <v>7347900</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4960600</v>
+        <v>300384700</v>
       </c>
       <c r="E52" s="3">
-        <v>4937800</v>
+        <v>272520700</v>
       </c>
       <c r="F52" s="3">
-        <v>3867500</v>
+        <v>331982100</v>
       </c>
       <c r="G52" s="3">
-        <v>3564200</v>
+        <v>304494600</v>
       </c>
       <c r="H52" s="3">
-        <v>3367000</v>
+        <v>279375700</v>
       </c>
       <c r="I52" s="3">
-        <v>3178500</v>
+        <v>243599300</v>
       </c>
       <c r="J52" s="3">
-        <v>3363300</v>
+        <v>274442600</v>
       </c>
       <c r="K52" s="3">
         <v>3227200</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>644519000</v>
+        <v>662997200</v>
       </c>
       <c r="E54" s="3">
-        <v>613687000</v>
+        <v>615986900</v>
       </c>
       <c r="F54" s="3">
-        <v>675486000</v>
+        <v>725128600</v>
       </c>
       <c r="G54" s="3">
-        <v>648034000</v>
+        <v>690903300</v>
       </c>
       <c r="H54" s="3">
-        <v>595609000</v>
+        <v>623830500</v>
       </c>
       <c r="I54" s="3">
-        <v>552282000</v>
+        <v>549834400</v>
       </c>
       <c r="J54" s="3">
-        <v>537017000</v>
+        <v>581727600</v>
       </c>
       <c r="K54" s="3">
         <v>523942000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>2143700</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+        <v>1766600</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>75700</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2718,13 +2718,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>500400</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>319000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>575493000</v>
+        <v>12843100</v>
       </c>
       <c r="E59" s="3">
-        <v>810163000</v>
+        <v>144100</v>
       </c>
       <c r="F59" s="3">
-        <v>320767000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>296726000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>278600000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>255192000</v>
-      </c>
-      <c r="J59" s="3">
-        <v>261338000</v>
+        <v>282100</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K59" s="3">
         <v>251392000</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>15062500</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1910700</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
-      </c>
-      <c r="G60" s="3">
-        <v>0</v>
+        <v>282100</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3">
-        <v>0</v>
+        <v>500400</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>319000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>9376600</v>
+        <v>16782900</v>
       </c>
       <c r="E61" s="3">
-        <v>9095400</v>
+        <v>18014400</v>
       </c>
       <c r="F61" s="3">
-        <v>8731700</v>
+        <v>15560000</v>
       </c>
       <c r="G61" s="3">
-        <v>10300400</v>
+        <v>20911200</v>
       </c>
       <c r="H61" s="3">
-        <v>8887100</v>
+        <v>14965700</v>
       </c>
       <c r="I61" s="3">
-        <v>9938200</v>
+        <v>14155700</v>
       </c>
       <c r="J61" s="3">
-        <v>9696000</v>
+        <v>15214300</v>
       </c>
       <c r="K61" s="3">
         <v>9361000</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1249200</v>
+        <v>592970000</v>
       </c>
       <c r="E62" s="3">
-        <v>1130700</v>
+        <v>559294200</v>
       </c>
       <c r="F62" s="3">
-        <v>2038300</v>
+        <v>660579700</v>
       </c>
       <c r="G62" s="3">
-        <v>1924200</v>
+        <v>626341200</v>
       </c>
       <c r="H62" s="3">
-        <v>1451600</v>
+        <v>568212900</v>
       </c>
       <c r="I62" s="3">
-        <v>1335300</v>
+        <v>499794800</v>
       </c>
       <c r="J62" s="3">
-        <v>943000</v>
+        <v>531552200</v>
       </c>
       <c r="K62" s="3">
         <v>988000</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>609704000</v>
+        <v>626100400</v>
       </c>
       <c r="E66" s="3">
-        <v>579238000</v>
+        <v>580354200</v>
       </c>
       <c r="F66" s="3">
-        <v>633399000</v>
+        <v>678609900</v>
       </c>
       <c r="G66" s="3">
-        <v>610087000</v>
+        <v>649303900</v>
       </c>
       <c r="H66" s="3">
-        <v>559617000</v>
+        <v>585199300</v>
       </c>
       <c r="I66" s="3">
-        <v>518378000</v>
+        <v>515279900</v>
       </c>
       <c r="J66" s="3">
-        <v>506664000</v>
+        <v>548107000</v>
       </c>
       <c r="K66" s="3">
         <v>493350000</v>
@@ -3220,25 +3220,25 @@
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>4902500</v>
+        <v>1892300</v>
       </c>
       <c r="E70" s="3">
-        <v>4902500</v>
+        <v>1846400</v>
       </c>
       <c r="F70" s="3">
-        <v>4697100</v>
+        <v>2536600</v>
       </c>
       <c r="G70" s="3">
-        <v>2813400</v>
+        <v>2999500</v>
       </c>
       <c r="H70" s="3">
-        <v>2813400</v>
+        <v>2946700</v>
       </c>
       <c r="I70" s="3">
-        <v>2813400</v>
+        <v>2800900</v>
       </c>
       <c r="J70" s="3">
-        <v>2633100</v>
+        <v>2852300</v>
       </c>
       <c r="K70" s="3">
         <v>2600500</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3547300</v>
+        <v>3649000</v>
       </c>
       <c r="E72" s="3">
-        <v>2905400</v>
+        <v>2916300</v>
       </c>
       <c r="F72" s="3">
-        <v>17292700</v>
+        <v>18563600</v>
       </c>
       <c r="G72" s="3">
-        <v>13902900</v>
+        <v>14822600</v>
       </c>
       <c r="H72" s="3">
-        <v>11400900</v>
+        <v>11941100</v>
       </c>
       <c r="I72" s="3">
-        <v>9351500</v>
+        <v>9310100</v>
       </c>
       <c r="J72" s="3">
-        <v>7422200</v>
+        <v>8040200</v>
       </c>
       <c r="K72" s="3">
         <v>7094900</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>29912600</v>
+        <v>33920900</v>
       </c>
       <c r="E76" s="3">
-        <v>29546700</v>
+        <v>32731900</v>
       </c>
       <c r="F76" s="3">
-        <v>37390000</v>
+        <v>42643600</v>
       </c>
       <c r="G76" s="3">
-        <v>35133800</v>
+        <v>37458000</v>
       </c>
       <c r="H76" s="3">
-        <v>33178700</v>
+        <v>34750800</v>
       </c>
       <c r="I76" s="3">
-        <v>31090400</v>
+        <v>30952600</v>
       </c>
       <c r="J76" s="3">
-        <v>27719700</v>
+        <v>30027600</v>
       </c>
       <c r="K76" s="3">
         <v>27992100</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>3533300</v>
+        <v>4136700</v>
       </c>
       <c r="E81" s="3">
-        <v>-1614300</v>
+        <v>-1551600</v>
       </c>
       <c r="F81" s="3">
-        <v>5071800</v>
+        <v>5260400</v>
       </c>
       <c r="G81" s="3">
-        <v>4195800</v>
+        <v>4179900</v>
       </c>
       <c r="H81" s="3">
-        <v>3997100</v>
+        <v>4062300</v>
       </c>
       <c r="I81" s="3">
-        <v>3409700</v>
+        <v>3424600</v>
       </c>
       <c r="J81" s="3">
-        <v>1431700</v>
+        <v>1649000</v>
       </c>
       <c r="K81" s="3">
         <v>2032700</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>427700</v>
+        <v>191600</v>
       </c>
       <c r="E83" s="3">
-        <v>382000</v>
+        <v>129300</v>
       </c>
       <c r="F83" s="3">
-        <v>389400</v>
+        <v>223600</v>
       </c>
       <c r="G83" s="3">
-        <v>482900</v>
+        <v>288000</v>
       </c>
       <c r="H83" s="3">
-        <v>460800</v>
+        <v>273700</v>
       </c>
       <c r="I83" s="3">
-        <v>549900</v>
+        <v>360600</v>
       </c>
       <c r="J83" s="3">
-        <v>412200</v>
+        <v>263900</v>
       </c>
       <c r="K83" s="3">
         <v>503800</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>15033600</v>
+        <v>15464600</v>
       </c>
       <c r="E89" s="3">
-        <v>12240000</v>
+        <v>12285900</v>
       </c>
       <c r="F89" s="3">
-        <v>17044600</v>
+        <v>18297300</v>
       </c>
       <c r="G89" s="3">
-        <v>14757500</v>
+        <v>15733800</v>
       </c>
       <c r="H89" s="3">
-        <v>15121200</v>
+        <v>15837700</v>
       </c>
       <c r="I89" s="3">
-        <v>14124500</v>
+        <v>14061900</v>
       </c>
       <c r="J89" s="3">
-        <v>13096100</v>
+        <v>14186500</v>
       </c>
       <c r="K89" s="3">
         <v>12385300</v>
@@ -4027,26 +4027,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-10099400</v>
+        <v>-10389000</v>
       </c>
       <c r="E94" s="3">
-        <v>-13544400</v>
+        <v>-13595200</v>
       </c>
       <c r="F94" s="3">
-        <v>-17992000</v>
+        <v>-19314300</v>
       </c>
       <c r="G94" s="3">
-        <v>-10414500</v>
+        <v>-11103400</v>
       </c>
       <c r="H94" s="3">
-        <v>-10180400</v>
+        <v>-10662800</v>
       </c>
       <c r="I94" s="3">
-        <v>-13987600</v>
+        <v>-13925600</v>
       </c>
       <c r="J94" s="3">
-        <v>-11989000</v>
+        <v>-12987200</v>
       </c>
       <c r="K94" s="3">
         <v>-16531500</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2187700</v>
+        <v>2021000</v>
       </c>
       <c r="E96" s="3">
-        <v>-2051500</v>
+        <v>1856800</v>
       </c>
       <c r="F96" s="3">
-        <v>-1840300</v>
+        <v>1795400</v>
       </c>
       <c r="G96" s="3">
-        <v>-1722500</v>
+        <v>1702200</v>
       </c>
       <c r="H96" s="3">
-        <v>-1029100</v>
+        <v>945200</v>
       </c>
       <c r="I96" s="3">
-        <v>-1316200</v>
+        <v>1187200</v>
       </c>
       <c r="J96" s="3">
-        <v>-1310300</v>
+        <v>1292600</v>
       </c>
       <c r="K96" s="3">
         <v>-1158100</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-3711500</v>
+        <v>-3817900</v>
       </c>
       <c r="E100" s="3">
-        <v>-1551700</v>
+        <v>-1557500</v>
       </c>
       <c r="F100" s="3">
-        <v>-1506800</v>
+        <v>-1617600</v>
       </c>
       <c r="G100" s="3">
-        <v>488000</v>
+        <v>520300</v>
       </c>
       <c r="H100" s="3">
-        <v>-1531100</v>
+        <v>-1603700</v>
       </c>
       <c r="I100" s="3">
-        <v>-532900</v>
+        <v>-530600</v>
       </c>
       <c r="J100" s="3">
-        <v>10300</v>
+        <v>11200</v>
       </c>
       <c r="K100" s="3">
         <v>2389000</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-303300</v>
+        <v>-312000</v>
       </c>
       <c r="E101" s="3">
-        <v>430600</v>
+        <v>432200</v>
       </c>
       <c r="F101" s="3">
-        <v>-234800</v>
+        <v>-252100</v>
       </c>
       <c r="G101" s="3">
-        <v>-388700</v>
+        <v>-414400</v>
       </c>
       <c r="H101" s="3">
-        <v>-343000</v>
+        <v>-359300</v>
       </c>
       <c r="I101" s="3">
-        <v>605100</v>
+        <v>602400</v>
       </c>
       <c r="J101" s="3">
-        <v>-484400</v>
+        <v>-524700</v>
       </c>
       <c r="K101" s="3">
         <v>-252300</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>919400</v>
+        <v>945800</v>
       </c>
       <c r="E102" s="3">
-        <v>-2425500</v>
+        <v>-2434600</v>
       </c>
       <c r="F102" s="3">
-        <v>-2689000</v>
+        <v>-2886600</v>
       </c>
       <c r="G102" s="3">
-        <v>4442400</v>
+        <v>4736300</v>
       </c>
       <c r="H102" s="3">
-        <v>3066600</v>
+        <v>3211900</v>
       </c>
       <c r="I102" s="3">
-        <v>209100</v>
+        <v>208100</v>
       </c>
       <c r="J102" s="3">
-        <v>633100</v>
+        <v>685800</v>
       </c>
       <c r="K102" s="3">
         <v>-2009500</v>

--- a/AAII_Financials/Yearly/MFC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MFC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>MFC</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>20844600</v>
+      </c>
+      <c r="E8" s="3">
         <v>20631100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12495000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>47286800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>60525000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>59999900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>27308800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>45228400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>38776500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>24639500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>42697300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14348700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21913700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>39166700</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9988600</v>
+      </c>
+      <c r="E9" s="3">
         <v>10261800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9844700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>32956400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>52221800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>48940100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>23333900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>34461900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>28237800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16076700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>32633000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5127800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14975300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>32666700</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10856000</v>
+      </c>
+      <c r="E10" s="3">
         <v>10369300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2650300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>14330400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8303200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11059800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3975000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10766500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10538700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8562800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10064300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9220900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6938500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6500000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,24 +979,27 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>103600</v>
+      </c>
+      <c r="E14" s="3">
         <v>40900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>19200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>118500</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
@@ -993,51 +1012,54 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>150600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>510900</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>229400</v>
+        <v>425300</v>
       </c>
       <c r="E15" s="3">
-        <v>223900</v>
+        <v>275600</v>
       </c>
       <c r="F15" s="3">
+        <v>209800</v>
+      </c>
+      <c r="G15" s="3">
         <v>301100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>366500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>353100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>439700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>350100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14645100</v>
+      </c>
+      <c r="E17" s="3">
         <v>14527900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14017800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>39949000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>54284300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>54187400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>22329900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>42325800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>35619900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21847000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>38462000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10659700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>20274900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>38093500</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6199400</v>
+      </c>
+      <c r="E18" s="3">
         <v>6103100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1522800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7337900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6240800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5812500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4979000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2902500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3156700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2792400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4235300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3689000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1638800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1073200</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,8 +1211,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1205,8 +1238,8 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1223,189 +1256,204 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6332600</v>
+        <v>6624800</v>
       </c>
       <c r="E21" s="3">
-        <v>-1298900</v>
+        <v>6378800</v>
       </c>
       <c r="F21" s="3">
+        <v>-1313000</v>
+      </c>
+      <c r="G21" s="3">
         <v>7638900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6607300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6165600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5418700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3252600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3663300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3221300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4596700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4016300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1932500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1339500</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1168300</v>
+      </c>
+      <c r="E22" s="3">
         <v>1176700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>776600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>798900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>926900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1016900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>934400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>908200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>736500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>826700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>887900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>804500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>703100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>959500</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4927600</v>
+      </c>
+      <c r="E23" s="3">
         <v>4885500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2318600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6420400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5313900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4795600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4044600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1994300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2420200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1965800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3347500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2884500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>935700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>113700</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>842300</v>
+      </c>
+      <c r="E24" s="3">
         <v>639800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-856300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>958500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>937800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>553600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>463200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>190600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>142500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>246300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>529900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>463400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-319200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-74500</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4085200</v>
+      </c>
+      <c r="E26" s="3">
         <v>4245700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1462200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5461900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4376100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4242000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3581400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1803700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2277700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1719500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2817500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2421100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1254900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>188200</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3526400</v>
+      </c>
+      <c r="E27" s="3">
         <v>3634600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1620300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5444500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4473400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4186500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3394600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1550900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2032700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1558000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2646400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2292500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1227000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>33800</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1610,27 +1670,30 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29" s="3">
         <v>3100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>16200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>51200</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,9 +1784,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1745,8 +1814,8 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -1763,54 +1832,60 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3913600</v>
+      </c>
+      <c r="E33" s="3">
         <v>4136700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1551600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5260400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4179900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4062300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3424600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1649000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2032700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1558000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2649500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2308700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1278200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>33800</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3913600</v>
+      </c>
+      <c r="E35" s="3">
         <v>4136700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1551600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5260400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4179900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4062300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3424600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1649000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2032700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1558000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2649500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2308700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1278200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>33800</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,80 +2072,84 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17923500</v>
+      </c>
+      <c r="E41" s="3">
         <v>15400200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14151600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17854000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20536000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15651100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11883100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12730400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11014900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13429100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16548100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10492600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10076800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9843300</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3609200</v>
+      </c>
+      <c r="E42" s="3">
         <v>4401700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4373400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>11830200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>20197000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12013600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8440900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>10602200</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2076,44 +2165,47 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>814500</v>
+      </c>
+      <c r="E43" s="3">
         <v>909400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1335900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1544100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1133300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1067800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1003300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>915400</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2121,9 +2213,12 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2148,8 +2243,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2166,36 +2261,39 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>45493600</v>
+      </c>
+      <c r="E45" s="3">
         <v>36393200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>37811600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>39314400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>39567600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>36798500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>34931200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>27760600</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2211,36 +2309,39 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>67840800</v>
+      </c>
+      <c r="E46" s="3">
         <v>57104600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>57672400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>70542600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>81433800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>65531000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>56258500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>52008600</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2256,81 +2357,87 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>240949700</v>
+      </c>
+      <c r="E47" s="3">
         <v>249097800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>230655700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>261048300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>245955900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>221822800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>196454500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>201071700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>222987000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>218787000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>194874000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>152474000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>155275000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>148586000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1858400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1961900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2107300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1431900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1451900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1484900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1477400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1021500</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2340,60 +2447,66 @@
       <c r="N48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7681200</v>
+      </c>
+      <c r="E49" s="3">
         <v>7806900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7772200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7834900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7792300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7690600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7399600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7846400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7347900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7046100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4287200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4078500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7698000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4180700</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>318416900</v>
+      </c>
+      <c r="E52" s="3">
         <v>300384700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>272520700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>331982100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>304494600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>279375700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>243599300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>274442600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3227200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3053700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2613400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2127000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2391600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1349800</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>680282700</v>
+      </c>
+      <c r="E54" s="3">
         <v>662997200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>615986900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>725128600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>690903300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>623830500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>549834400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>581727600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>523942000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>529088000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>454863000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>395401000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>365102000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>354905000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,20 +2784,21 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1855000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2143700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1766600</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>8</v>
       </c>
@@ -2681,8 +2811,8 @@
       <c r="J57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -2699,17 +2829,20 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>75700</v>
+        <v>73000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>449800</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -2718,17 +2851,17 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>500400</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>319000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2744,24 +2877,27 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>12843100</v>
+        <v>11222900</v>
       </c>
       <c r="E59" s="3">
+        <v>143900</v>
+      </c>
+      <c r="F59" s="3">
         <v>144100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>282100</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H59" s="3" t="s">
         <v>8</v>
       </c>
@@ -2771,54 +2907,57 @@
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>251392000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>258201000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>223771000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>191862000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>314510000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>296767000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>15062500</v>
+        <v>13150900</v>
       </c>
       <c r="E60" s="3">
+        <v>2737300</v>
+      </c>
+      <c r="F60" s="3">
         <v>1910700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>282100</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" s="3">
         <v>500400</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K60" s="3">
         <v>319000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2834,99 +2973,108 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>16782900</v>
+        <v>17628800</v>
       </c>
       <c r="E61" s="3">
+        <v>16143800</v>
+      </c>
+      <c r="F61" s="3">
         <v>18014400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15560000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>20911200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14965700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14155700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15214300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9361000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7169200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7309600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7051600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6736700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13169000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>592970000</v>
+        <v>611382100</v>
       </c>
       <c r="E62" s="3">
+        <v>605934300</v>
+      </c>
+      <c r="F62" s="3">
         <v>559294200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>660579700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>626341200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>568212900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>499794800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>531552200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>988000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>927300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>964000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>475000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>453900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>588500</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>643475300</v>
+      </c>
+      <c r="E66" s="3">
         <v>626100400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>580354200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>678609900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>649303900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>585199300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>515279900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>548107000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>493350000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>498043000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>428593000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>373340000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>346389000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>336111000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,54 +3377,60 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1736800</v>
+      </c>
+      <c r="E70" s="3">
         <v>1892300</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1846400</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>2536600</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>2999500</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>2946700</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>2800900</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>2852300</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>2600500</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>2022100</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>2114100</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>2073100</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>3759400</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>1392800</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3311000</v>
+      </c>
+      <c r="E72" s="3">
         <v>3649000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2916300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18563600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14822600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11941100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9310100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8040200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7094900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6305700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5985200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4075400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2451100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1921300</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>34083000</v>
+      </c>
+      <c r="E76" s="3">
         <v>33920900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>32731900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>42643600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>37458000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>34750800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>30952600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>30027600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>27992100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>29023000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24155200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19987600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14953500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17401200</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3913600</v>
+      </c>
+      <c r="E81" s="3">
         <v>4136700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1551600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5260400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4179900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4062300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3424600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1649000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2032700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1558000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2649500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2308700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1278200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>33800</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>344000</v>
+      </c>
+      <c r="E83" s="3">
         <v>191600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>129300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>223600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>288000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>273700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>360600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>263900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>503800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>435500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>362700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>327900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>293600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>265000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18413400</v>
+      </c>
+      <c r="E89" s="3">
         <v>15464600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12285900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>18297300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>15733800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15837700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>14061900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14186500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>12385300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7759400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8483300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7315600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8126400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8349100</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,8 +4241,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4048,8 +4268,8 @@
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -4066,9 +4286,12 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12829100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10389000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13595200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19314300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11103400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10662800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13925600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12987200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16531500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-10410700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3192000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8119300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8156500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8263900</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1979400</v>
+      </c>
+      <c r="E96" s="3">
         <v>2021000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1856800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1795400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1702200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>945200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1187200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1292600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1158100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1071500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-714400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-585800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-551800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-550800</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2900900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3817900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1557500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1617600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>520300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1603700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-530600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>11200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2389000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1506200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>16500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>537300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>557100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>503200</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>831900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-312000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>432200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-252100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-414400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-359300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>602400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-524700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-252300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1578300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>620200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>368700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-160300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>147500</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3515300</v>
+      </c>
+      <c r="E102" s="3">
         <v>945800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2434600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2886600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4736300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3211900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>208100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>685800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2009500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2579200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5927900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>102400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>366600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>736000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/MFC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MFC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>MFC</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22591000</v>
+      </c>
+      <c r="E8" s="3">
         <v>20844600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20631100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12495000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>47286800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>60525000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>59999900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>27308800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>45228400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>38776500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>24639500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>42697300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14348700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>21913700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>39166700</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>11454100</v>
+      </c>
+      <c r="E9" s="3">
         <v>9988600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10261800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9844700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>32956400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>52221800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>48940100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>23333900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>34461900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>28237800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16076700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>32633000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5127800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14975300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>32666700</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>11136900</v>
+      </c>
+      <c r="E10" s="3">
         <v>10856000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10369300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2650300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>14330400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8303200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11059800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3975000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10766500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10538700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8562800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>10064300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9220900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6938500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6500000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,27 +998,30 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E14" s="3">
         <v>103600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>40900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>19200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>118500</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1015,54 +1034,57 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>150600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>510900</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>454400</v>
+      </c>
+      <c r="E15" s="3">
         <v>425300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>275600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>209800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>301100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>366500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>353100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>439700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>350100</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16268500</v>
+      </c>
+      <c r="E17" s="3">
         <v>14645100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14527900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14017800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>39949000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>54284300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>54187400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>22329900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>42325800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>35619900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>21847000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>38462000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10659700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20274900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>38093500</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6322600</v>
+      </c>
+      <c r="E18" s="3">
         <v>6199400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6103100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1522800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7337900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6240800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5812500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4979000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2902500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3156700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2792400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4235300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3689000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1638800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1073200</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,8 +1244,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1241,8 +1274,8 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1259,201 +1292,216 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6776900</v>
+      </c>
+      <c r="E21" s="3">
         <v>6624800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6378800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1313000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7638900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6607300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6165600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5418700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3252600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3663300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3221300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4596700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4016300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1932500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1339500</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1115900</v>
+      </c>
+      <c r="E22" s="3">
         <v>1168300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1176700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>776600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>798900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>926900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1016900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>934400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>908200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>736500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>826700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>887900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>804500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>703100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>959500</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5173900</v>
+      </c>
+      <c r="E23" s="3">
         <v>4927600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4885500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2318600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6420400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5313900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4795600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4044600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1994300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2420200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1965800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3347500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2884500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>935700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>113700</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>754100</v>
+      </c>
+      <c r="E24" s="3">
         <v>842300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>639800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-856300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>958500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>937800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>553600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>463200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>190600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>142500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>246300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>529900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>463400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-319200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-74500</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4419700</v>
+      </c>
+      <c r="E26" s="3">
         <v>4085200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4245700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1462200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5461900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4376100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4242000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3581400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1803700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2277700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1719500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2817500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2421100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1254900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>188200</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3829700</v>
+      </c>
+      <c r="E27" s="3">
         <v>3526400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3634600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1620300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5444500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4473400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4186500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3394600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1550900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2032700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1558000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2646400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2292500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1227000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>33800</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1673,27 +1733,30 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O29" s="3">
         <v>3100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>16200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>51200</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,9 +1853,12 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1817,8 +1886,8 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -1835,57 +1904,63 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4217000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3913600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4136700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1551600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5260400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4179900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4062300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3424600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1649000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2032700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1558000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2649500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2308700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1278200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>33800</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4217000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3913600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4136700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1551600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5260400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4179900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4062300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3424600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1649000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2032700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1558000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2649500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2308700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1278200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>33800</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,86 +2158,90 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19475300</v>
+      </c>
+      <c r="E41" s="3">
         <v>17923500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15400200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14151600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17854000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20536000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15651100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11883100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12730400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11014900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13429100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16548100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10492600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10076800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9843300</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3940600</v>
+      </c>
+      <c r="E42" s="3">
         <v>3609200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4401700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4373400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>11830200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>20197000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>12013600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8440900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>10602200</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2168,47 +2257,50 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>870100</v>
+      </c>
+      <c r="E43" s="3">
         <v>814500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>909400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1335900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1544100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1133300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1067800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1003300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>915400</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2216,9 +2308,12 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2246,8 +2341,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2264,39 +2359,42 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>49816200</v>
+      </c>
+      <c r="E45" s="3">
         <v>45493600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>36393200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>37811600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>39314400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>39567600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>36798500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>34931200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>27760600</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2312,39 +2410,42 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>74102200</v>
+      </c>
+      <c r="E46" s="3">
         <v>67840800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>57104600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>57672400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>70542600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>81433800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>65531000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>56258500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>52008600</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2360,87 +2461,93 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>263061600</v>
+      </c>
+      <c r="E47" s="3">
         <v>240949700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>249097800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>230655700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>261048300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>245955900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>221822800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>196454500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>201071700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>222987000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>218787000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>194874000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>152474000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>155275000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>148586000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1918900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1858400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1961900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2107300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1431900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1451900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1484900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1477400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1021500</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>8</v>
       </c>
@@ -2450,63 +2557,69 @@
       <c r="O48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8988300</v>
+      </c>
+      <c r="E49" s="3">
         <v>7681200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7806900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7772200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7834900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7792300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7690600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7399600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7846400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7347900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7046100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4287200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4078500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7698000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4180700</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>351968500</v>
+      </c>
+      <c r="E52" s="3">
         <v>318416900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>300384700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>272520700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>331982100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>304494600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>279375700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>243599300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>274442600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3227200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3053700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2613400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2127000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2391600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1349800</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>747879800</v>
+      </c>
+      <c r="E54" s="3">
         <v>680282700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>662997200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>615986900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>725128600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>690903300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>623830500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>549834400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>581727600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>523942000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>529088000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>454863000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>395401000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>365102000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>354905000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,23 +2914,24 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2387100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1855000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2143700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1766600</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>8</v>
       </c>
@@ -2814,8 +2944,8 @@
       <c r="K57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -2832,21 +2962,24 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>73000</v>
+        <v>73700</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>449800</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -2854,17 +2987,17 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>500400</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>319000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -2880,27 +3013,30 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>11222900</v>
+        <v>13189900</v>
       </c>
       <c r="E59" s="3">
+        <v>318300</v>
+      </c>
+      <c r="F59" s="3">
         <v>143900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>144100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>282100</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>8</v>
       </c>
@@ -2910,57 +3046,60 @@
       <c r="K59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3">
         <v>251392000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>258201000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>223771000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>191862000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>314510000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>296767000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>13150900</v>
+        <v>15650700</v>
       </c>
       <c r="E60" s="3">
+        <v>2173300</v>
+      </c>
+      <c r="F60" s="3">
         <v>2737300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1910700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>282100</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="I60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J60" s="3">
         <v>500400</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L60" s="3">
         <v>319000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2976,105 +3115,114 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>17628800</v>
+        <v>18433800</v>
       </c>
       <c r="E61" s="3">
+        <v>17455000</v>
+      </c>
+      <c r="F61" s="3">
         <v>16143800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18014400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15560000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>20911200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14965700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14155700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15214300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9361000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7169200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7309600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7051600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6736700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13169000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>611382100</v>
+        <v>674042400</v>
       </c>
       <c r="E62" s="3">
+        <v>622533400</v>
+      </c>
+      <c r="F62" s="3">
         <v>605934300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>559294200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>660579700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>626341200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>568212900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>499794800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>531552200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>988000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>927300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>964000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>475000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>453900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>588500</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>709598700</v>
+      </c>
+      <c r="E66" s="3">
         <v>643475300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>626100400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>580354200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>678609900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>649303900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>585199300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>515279900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>548107000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>493350000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>498043000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>428593000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>373340000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>346389000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>336111000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,57 +3544,63 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1822600</v>
+      </c>
+      <c r="E70" s="3">
         <v>1736800</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1892300</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>1846400</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>2536600</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>2999500</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>2946700</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>2800900</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>2852300</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>2600500</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>2022100</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>2114100</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>2073100</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>3759400</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>1392800</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3664200</v>
+      </c>
+      <c r="E72" s="3">
         <v>3311000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3649000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2916300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18563600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>14822600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11941100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9310100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8040200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7094900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6305700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5985200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4075400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2451100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1921300</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>35341900</v>
+      </c>
+      <c r="E76" s="3">
         <v>34083000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>33920900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>32731900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>42643600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>37458000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>34750800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>30952600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>30027600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>27992100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>29023000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>24155200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19987600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14953500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17401200</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4217000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3913600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4136700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1551600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5260400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4179900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4062300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3424600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1649000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2032700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1558000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2649500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2308700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1278200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>33800</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>374100</v>
+      </c>
+      <c r="E83" s="3">
         <v>344000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>191600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>129300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>223600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>288000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>273700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>360600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>263900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>503800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>435500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>362700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>327900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>293600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>265000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>23415200</v>
+      </c>
+      <c r="E89" s="3">
         <v>18413400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15464600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>12285900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>18297300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15733800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>15837700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14061900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>14186500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12385300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7759400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8483300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7315600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8126400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>8349100</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,8 +4461,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4271,8 +4491,8 @@
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -4289,9 +4509,12 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-20687500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12829100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10389000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13595200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-19314300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11103400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10662800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13925600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12987200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16531500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10410700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3192000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8119300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8156500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8263900</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2176300</v>
+      </c>
+      <c r="E96" s="3">
         <v>1979400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2021000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1856800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1795400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1702200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>945200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1187200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1292600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1158100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1071500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-714400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-585800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-551800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-550800</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1494400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2900900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3817900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1557500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1617600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>520300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1603700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-530600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>11200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2389000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1506200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>16500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>537300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>557100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>503200</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-595100</v>
+      </c>
+      <c r="E101" s="3">
         <v>831900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-312000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>432200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-252100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-414400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-359300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>602400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-524700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-252300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1578300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>620200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>368700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-160300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>147500</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>638200</v>
+      </c>
+      <c r="E102" s="3">
         <v>3515300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>945800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2434600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2886600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4736300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3211900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>208100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>685800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2009500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2579200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5927900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>102400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>366600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>736000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
